--- a/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_telecom_wireless.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2234558088381118</v>
+        <v>0.223113283963087</v>
       </c>
       <c r="C2">
-        <v>229.764190744753</v>
+        <v>227.6692149044431</v>
       </c>
       <c r="D2">
-        <v>117.164190744753</v>
+        <v>117.3458149044431</v>
       </c>
       <c r="E2">
-        <v>-7.86</v>
+        <v>-5.5834</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.2766</v>
       </c>
       <c r="G2">
         <v>112.6</v>
@@ -1439,28 +1439,28 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.11451298</v>
       </c>
       <c r="N2">
-        <v>9.100000000000001</v>
+        <v>8.985487020000001</v>
       </c>
       <c r="O2">
-        <v>1.547</v>
+        <v>1.5275327934</v>
       </c>
       <c r="P2">
-        <v>7.553000000000001</v>
+        <v>7.4579542266</v>
       </c>
       <c r="Q2">
-        <v>30.953</v>
+        <v>30.8579542266</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2234558088381118</v>
+        <v>0.2249452464273606</v>
       </c>
       <c r="T2">
-        <v>0.6362422799549506</v>
+        <v>0.6415764324030578</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>79.46697396225302</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.223113283963087</v>
+        <v>0.2227707590880622</v>
       </c>
       <c r="C3">
-        <v>227.6692149044431</v>
+        <v>225.5748030342418</v>
       </c>
       <c r="D3">
-        <v>117.3458149044431</v>
+        <v>117.5280030342418</v>
       </c>
       <c r="E3">
-        <v>-5.5834</v>
+        <v>-3.3068</v>
       </c>
       <c r="F3">
-        <v>2.2766</v>
+        <v>4.5532</v>
       </c>
       <c r="G3">
         <v>112.6</v>
@@ -1521,28 +1521,28 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M3">
-        <v>0.11451298</v>
+        <v>0.22902596</v>
       </c>
       <c r="N3">
-        <v>8.985487020000001</v>
+        <v>8.870974040000002</v>
       </c>
       <c r="O3">
-        <v>1.5275327934</v>
+        <v>1.5080655868</v>
       </c>
       <c r="P3">
-        <v>7.4579542266</v>
+        <v>7.362908453200001</v>
       </c>
       <c r="Q3">
-        <v>30.8579542266</v>
+        <v>30.7629084532</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2249452464273606</v>
+        <v>0.2264650807021043</v>
       </c>
       <c r="T3">
-        <v>0.6415764324030578</v>
+        <v>0.647019445105208</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>79.46697396225302</v>
+        <v>39.73348698112652</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2227707590880622</v>
+        <v>0.2224282342130374</v>
       </c>
       <c r="C4">
-        <v>225.5748030342418</v>
+        <v>223.4809577650506</v>
       </c>
       <c r="D4">
-        <v>117.5280030342418</v>
+        <v>117.7107577650506</v>
       </c>
       <c r="E4">
-        <v>-3.3068</v>
+        <v>-1.0302</v>
       </c>
       <c r="F4">
-        <v>4.5532</v>
+        <v>6.829800000000001</v>
       </c>
       <c r="G4">
         <v>112.6</v>
@@ -1603,28 +1603,28 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M4">
-        <v>0.22902596</v>
+        <v>0.34353894</v>
       </c>
       <c r="N4">
-        <v>8.870974040000002</v>
+        <v>8.756461060000001</v>
       </c>
       <c r="O4">
-        <v>1.5080655868</v>
+        <v>1.4885983802</v>
       </c>
       <c r="P4">
-        <v>7.362908453200001</v>
+        <v>7.267862679800001</v>
       </c>
       <c r="Q4">
-        <v>30.7629084532</v>
+        <v>30.6678626798</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2264650807021043</v>
+        <v>0.2280162517660179</v>
       </c>
       <c r="T4">
-        <v>0.647019445105208</v>
+        <v>0.6525746848733819</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>39.73348698112652</v>
+        <v>26.48899132075101</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2224282342130374</v>
+        <v>0.2220857093380126</v>
       </c>
       <c r="C5">
-        <v>223.4809577650506</v>
+        <v>221.3876817441607</v>
       </c>
       <c r="D5">
-        <v>117.7107577650506</v>
+        <v>117.8940817441607</v>
       </c>
       <c r="E5">
-        <v>-1.0302</v>
+        <v>1.2464</v>
       </c>
       <c r="F5">
-        <v>6.829800000000001</v>
+        <v>9.106400000000001</v>
       </c>
       <c r="G5">
         <v>112.6</v>
@@ -1685,28 +1685,28 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M5">
-        <v>0.34353894</v>
+        <v>0.45805192</v>
       </c>
       <c r="N5">
-        <v>8.756461060000001</v>
+        <v>8.641948080000001</v>
       </c>
       <c r="O5">
-        <v>1.4885983802</v>
+        <v>1.4691311736</v>
       </c>
       <c r="P5">
-        <v>7.267862679800001</v>
+        <v>7.1728169064</v>
       </c>
       <c r="Q5">
-        <v>30.6678626798</v>
+        <v>30.5728169064</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2280162517660179</v>
+        <v>0.2295997388937631</v>
       </c>
       <c r="T5">
-        <v>0.6525746848733819</v>
+        <v>0.6582456588033927</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>26.48899132075101</v>
+        <v>19.86674349056326</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2220857093380126</v>
+        <v>0.2217431844629878</v>
       </c>
       <c r="C6">
-        <v>221.3876817441607</v>
+        <v>219.2949776353808</v>
       </c>
       <c r="D6">
-        <v>117.8940817441607</v>
+        <v>118.0779776353808</v>
       </c>
       <c r="E6">
-        <v>1.2464</v>
+        <v>3.523000000000002</v>
       </c>
       <c r="F6">
-        <v>9.106400000000001</v>
+        <v>11.383</v>
       </c>
       <c r="G6">
         <v>112.6</v>
@@ -1767,28 +1767,28 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M6">
-        <v>0.45805192</v>
+        <v>0.5725649000000002</v>
       </c>
       <c r="N6">
-        <v>8.641948080000001</v>
+        <v>8.527435100000002</v>
       </c>
       <c r="O6">
-        <v>1.4691311736</v>
+        <v>1.449663967</v>
       </c>
       <c r="P6">
-        <v>7.1728169064</v>
+        <v>7.077771133000001</v>
       </c>
       <c r="Q6">
-        <v>30.5728169064</v>
+        <v>30.477771133</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2295997388937631</v>
+        <v>0.2312165625926187</v>
       </c>
       <c r="T6">
-        <v>0.6582456588033927</v>
+        <v>0.6640360216582458</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>19.86674349056326</v>
+        <v>15.8933947924506</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2217431844629878</v>
+        <v>0.221400659587963</v>
       </c>
       <c r="C7">
-        <v>219.2949776353808</v>
+        <v>217.2028481191658</v>
       </c>
       <c r="D7">
-        <v>118.0779776353808</v>
+        <v>118.2624481191658</v>
       </c>
       <c r="E7">
-        <v>3.523000000000002</v>
+        <v>5.799600000000003</v>
       </c>
       <c r="F7">
-        <v>11.383</v>
+        <v>13.6596</v>
       </c>
       <c r="G7">
         <v>112.6</v>
@@ -1849,28 +1849,28 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M7">
-        <v>0.5725649000000002</v>
+        <v>0.6870778800000001</v>
       </c>
       <c r="N7">
-        <v>8.527435100000002</v>
+        <v>8.412922120000001</v>
       </c>
       <c r="O7">
-        <v>1.449663967</v>
+        <v>1.4301967604</v>
       </c>
       <c r="P7">
-        <v>7.077771133000001</v>
+        <v>6.982725359600001</v>
       </c>
       <c r="Q7">
-        <v>30.477771133</v>
+        <v>30.3827253596</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2312165625926187</v>
+        <v>0.2328677867957053</v>
       </c>
       <c r="T7">
-        <v>0.6640360216582458</v>
+        <v>0.6699495837227768</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>15.8933947924506</v>
+        <v>13.2444956603755</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.221400659587963</v>
+        <v>0.2211452847129382</v>
       </c>
       <c r="C8">
-        <v>217.2028481191658</v>
+        <v>215.0641585288311</v>
       </c>
       <c r="D8">
-        <v>118.2624481191658</v>
+        <v>118.4003585288311</v>
       </c>
       <c r="E8">
-        <v>5.799600000000001</v>
+        <v>8.0762</v>
       </c>
       <c r="F8">
-        <v>13.6596</v>
+        <v>15.9362</v>
       </c>
       <c r="G8">
         <v>112.6</v>
@@ -1931,45 +1931,45 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M8">
-        <v>0.68707788</v>
+        <v>0.82549516</v>
       </c>
       <c r="N8">
-        <v>8.412922120000001</v>
+        <v>8.274504840000002</v>
       </c>
       <c r="O8">
-        <v>1.4301967604</v>
+        <v>1.4066658228</v>
       </c>
       <c r="P8">
-        <v>6.982725359600001</v>
+        <v>6.867839017200001</v>
       </c>
       <c r="Q8">
-        <v>30.3827253596</v>
+        <v>30.2678390172</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2328677867957053</v>
+        <v>0.2345545211967077</v>
       </c>
       <c r="T8">
-        <v>0.6699495837227768</v>
+        <v>0.6759903191650395</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.17</v>
       </c>
       <c r="W8">
-        <v>0.04174899999999999</v>
+        <v>0.042994</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>13.2444956603755</v>
+        <v>11.0236866803677</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.2211452847129382</v>
+        <v>0.2209280898379134</v>
       </c>
       <c r="C9">
-        <v>215.0641585288311</v>
+        <v>212.9051039054488</v>
       </c>
       <c r="D9">
-        <v>118.4003585288311</v>
+        <v>118.5179039054488</v>
       </c>
       <c r="E9">
-        <v>8.076200000000004</v>
+        <v>10.3528</v>
       </c>
       <c r="F9">
-        <v>15.9362</v>
+        <v>18.2128</v>
       </c>
       <c r="G9">
         <v>112.6</v>
@@ -2013,45 +2013,45 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M9">
-        <v>0.8254951600000001</v>
+        <v>0.9743848000000001</v>
       </c>
       <c r="N9">
-        <v>8.274504840000001</v>
+        <v>8.125615200000002</v>
       </c>
       <c r="O9">
-        <v>1.4066658228</v>
+        <v>1.381354584000001</v>
       </c>
       <c r="P9">
-        <v>6.867839017200001</v>
+        <v>6.744260616000002</v>
       </c>
       <c r="Q9">
-        <v>30.2678390172</v>
+        <v>30.144260616</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2345545211967077</v>
+        <v>0.2362779237368624</v>
       </c>
       <c r="T9">
-        <v>0.6759903191650395</v>
+        <v>0.6821623749430036</v>
       </c>
       <c r="U9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V9">
         <v>0.17</v>
       </c>
       <c r="W9">
-        <v>0.042994</v>
+        <v>0.044405</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>11.02368668036769</v>
+        <v>9.339226145563849</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2209280898379134</v>
+        <v>0.2206121249628887</v>
       </c>
       <c r="C10">
-        <v>212.9051039054488</v>
+        <v>210.7999207164072</v>
       </c>
       <c r="D10">
-        <v>118.5179039054488</v>
+        <v>118.6893207164072</v>
       </c>
       <c r="E10">
-        <v>10.3528</v>
+        <v>12.6294</v>
       </c>
       <c r="F10">
-        <v>18.2128</v>
+        <v>20.4894</v>
       </c>
       <c r="G10">
         <v>112.6</v>
@@ -2095,28 +2095,28 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M10">
-        <v>0.9743848000000001</v>
+        <v>1.0961829</v>
       </c>
       <c r="N10">
-        <v>8.125615200000002</v>
+        <v>8.003817100000001</v>
       </c>
       <c r="O10">
-        <v>1.381354584000001</v>
+        <v>1.360648907</v>
       </c>
       <c r="P10">
-        <v>6.744260616000002</v>
+        <v>6.643168193000001</v>
       </c>
       <c r="Q10">
-        <v>30.144260616</v>
+        <v>30.043168193</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2362779237368624</v>
+        <v>0.2380392032559216</v>
       </c>
       <c r="T10">
-        <v>0.6821623749430036</v>
+        <v>0.6884700802985054</v>
       </c>
       <c r="U10">
         <v>0.0535</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>9.339226145563849</v>
+        <v>8.301534351612309</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.2206121249628887</v>
+        <v>0.2203625600878638</v>
       </c>
       <c r="C11">
-        <v>210.7999207164072</v>
+        <v>208.659065192321</v>
       </c>
       <c r="D11">
-        <v>118.6893207164072</v>
+        <v>118.825065192321</v>
       </c>
       <c r="E11">
-        <v>12.6294</v>
+        <v>14.906</v>
       </c>
       <c r="F11">
-        <v>20.4894</v>
+        <v>22.766</v>
       </c>
       <c r="G11">
         <v>112.6</v>
@@ -2177,45 +2177,45 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M11">
-        <v>1.0961829</v>
+        <v>1.2361938</v>
       </c>
       <c r="N11">
-        <v>8.003817100000001</v>
+        <v>7.863806200000001</v>
       </c>
       <c r="O11">
-        <v>1.360648907</v>
+        <v>1.336847054</v>
       </c>
       <c r="P11">
-        <v>6.643168193000001</v>
+        <v>6.526959146000001</v>
       </c>
       <c r="Q11">
-        <v>30.043168193</v>
+        <v>29.926959146</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2380392032559216</v>
+        <v>0.2398396223198487</v>
       </c>
       <c r="T11">
-        <v>0.6884700802985054</v>
+        <v>0.6949179568841294</v>
       </c>
       <c r="U11">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V11">
         <v>0.17</v>
       </c>
       <c r="W11">
-        <v>0.044405</v>
+        <v>0.045069</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y11">
-        <v>8.301534351612309</v>
+        <v>7.361305322838539</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.2203625600878638</v>
+        <v>0.2200532352128391</v>
       </c>
       <c r="C12">
-        <v>208.659065192321</v>
+        <v>206.5511461443552</v>
       </c>
       <c r="D12">
-        <v>118.825065192321</v>
+        <v>118.9937461443553</v>
       </c>
       <c r="E12">
-        <v>14.90600000000001</v>
+        <v>17.1826</v>
       </c>
       <c r="F12">
-        <v>22.76600000000001</v>
+        <v>25.0426</v>
       </c>
       <c r="G12">
         <v>112.6</v>
@@ -2259,28 +2259,28 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M12">
-        <v>1.2361938</v>
+        <v>1.35981318</v>
       </c>
       <c r="N12">
-        <v>7.863806200000001</v>
+        <v>7.740186820000002</v>
       </c>
       <c r="O12">
-        <v>1.336847054</v>
+        <v>1.3158317594</v>
       </c>
       <c r="P12">
-        <v>6.526959146000001</v>
+        <v>6.424355060600002</v>
       </c>
       <c r="Q12">
-        <v>29.926959146</v>
+        <v>29.8243550606</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2398396223198487</v>
+        <v>0.241680500239145</v>
       </c>
       <c r="T12">
-        <v>0.6949179568841294</v>
+        <v>0.7015107295728011</v>
       </c>
       <c r="U12">
         <v>0.0543</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>7.361305322838538</v>
+        <v>6.692095748035036</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.2200532352128391</v>
+        <v>0.2197439103378143</v>
       </c>
       <c r="C13">
-        <v>206.5511461443552</v>
+        <v>204.4437066873321</v>
       </c>
       <c r="D13">
-        <v>118.9937461443553</v>
+        <v>119.1629066873321</v>
       </c>
       <c r="E13">
-        <v>17.1826</v>
+        <v>19.4592</v>
       </c>
       <c r="F13">
-        <v>25.0426</v>
+        <v>27.3192</v>
       </c>
       <c r="G13">
         <v>112.6</v>
@@ -2341,28 +2341,28 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M13">
-        <v>1.35981318</v>
+        <v>1.48343256</v>
       </c>
       <c r="N13">
-        <v>7.740186820000002</v>
+        <v>7.616567440000001</v>
       </c>
       <c r="O13">
-        <v>1.3158317594</v>
+        <v>1.2948164648</v>
       </c>
       <c r="P13">
-        <v>6.424355060600002</v>
+        <v>6.321750975200001</v>
       </c>
       <c r="Q13">
-        <v>29.8243550606</v>
+        <v>29.7217509752</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.241680500239145</v>
+        <v>0.2435632162929708</v>
       </c>
       <c r="T13">
-        <v>0.7015107295728011</v>
+        <v>0.7082533380043974</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>6.692095748035036</v>
+        <v>6.134421102365448</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.2197439103378143</v>
+        <v>0.2195424854627895</v>
       </c>
       <c r="C14">
-        <v>204.4437066873321</v>
+        <v>202.2775187424638</v>
       </c>
       <c r="D14">
-        <v>119.1629066873321</v>
+        <v>119.2733187424638</v>
       </c>
       <c r="E14">
-        <v>19.4592</v>
+        <v>21.7358</v>
       </c>
       <c r="F14">
-        <v>27.3192</v>
+        <v>29.5958</v>
       </c>
       <c r="G14">
         <v>112.6</v>
@@ -2423,45 +2423,45 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M14">
-        <v>1.48343256</v>
+        <v>1.63664774</v>
       </c>
       <c r="N14">
-        <v>7.616567440000001</v>
+        <v>7.463352260000001</v>
       </c>
       <c r="O14">
-        <v>1.2948164648</v>
+        <v>1.2687698842</v>
       </c>
       <c r="P14">
-        <v>6.321750975200001</v>
+        <v>6.1945823758</v>
       </c>
       <c r="Q14">
-        <v>29.7217509752</v>
+        <v>29.5945823758</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2435632162929708</v>
+        <v>0.2454892131756201</v>
       </c>
       <c r="T14">
-        <v>0.7082533380043974</v>
+        <v>0.7151509489286738</v>
       </c>
       <c r="U14">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V14">
         <v>0.17</v>
       </c>
       <c r="W14">
-        <v>0.045069</v>
+        <v>0.045899</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>6.134421102365448</v>
+        <v>5.560145764781369</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.2195424854627895</v>
+        <v>0.2192414605877647</v>
       </c>
       <c r="C15">
-        <v>202.2775187424638</v>
+        <v>200.1663089482622</v>
       </c>
       <c r="D15">
-        <v>119.2733187424638</v>
+        <v>119.4387089482622</v>
       </c>
       <c r="E15">
-        <v>21.7358</v>
+        <v>24.01240000000001</v>
       </c>
       <c r="F15">
-        <v>29.5958</v>
+        <v>31.87240000000001</v>
       </c>
       <c r="G15">
         <v>112.6</v>
@@ -2505,28 +2505,28 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M15">
-        <v>1.63664774</v>
+        <v>1.76254372</v>
       </c>
       <c r="N15">
-        <v>7.463352260000001</v>
+        <v>7.337456280000001</v>
       </c>
       <c r="O15">
-        <v>1.2687698842</v>
+        <v>1.2473675676</v>
       </c>
       <c r="P15">
-        <v>6.1945823758</v>
+        <v>6.090088712400001</v>
       </c>
       <c r="Q15">
-        <v>29.5945823758</v>
+        <v>29.4900887124</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2454892131756201</v>
+        <v>0.2474600006834473</v>
       </c>
       <c r="T15">
-        <v>0.7151509489286738</v>
+        <v>0.7222089694093289</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.560145764781369</v>
+        <v>5.162992495868414</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.2192414605877647</v>
+        <v>0.2189404357127399</v>
       </c>
       <c r="C16">
-        <v>200.1663089482622</v>
+        <v>198.0555584672316</v>
       </c>
       <c r="D16">
-        <v>119.4387089482622</v>
+        <v>119.6045584672316</v>
       </c>
       <c r="E16">
-        <v>24.01240000000001</v>
+        <v>26.28900000000001</v>
       </c>
       <c r="F16">
-        <v>31.87240000000001</v>
+        <v>34.14900000000001</v>
       </c>
       <c r="G16">
         <v>112.6</v>
@@ -2587,28 +2587,28 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M16">
-        <v>1.76254372</v>
+        <v>1.888439700000001</v>
       </c>
       <c r="N16">
-        <v>7.337456280000001</v>
+        <v>7.2115603</v>
       </c>
       <c r="O16">
-        <v>1.2473675676</v>
+        <v>1.225965251</v>
       </c>
       <c r="P16">
-        <v>6.090088712400001</v>
+        <v>5.985595049000001</v>
       </c>
       <c r="Q16">
-        <v>29.4900887124</v>
+        <v>29.385595049</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2474600006834473</v>
+        <v>0.2494771596620469</v>
       </c>
       <c r="T16">
-        <v>0.7222089694093289</v>
+        <v>0.729433060960117</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.162992495868414</v>
+        <v>4.818792996143852</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.2189404357127399</v>
+        <v>0.218639410837715</v>
       </c>
       <c r="C17">
-        <v>198.0555584672316</v>
+        <v>195.945269215404</v>
       </c>
       <c r="D17">
-        <v>119.6045584672316</v>
+        <v>119.770869215404</v>
       </c>
       <c r="E17">
-        <v>26.289</v>
+        <v>28.5656</v>
       </c>
       <c r="F17">
-        <v>34.149</v>
+        <v>36.4256</v>
       </c>
       <c r="G17">
         <v>112.6</v>
@@ -2669,28 +2669,28 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M17">
-        <v>1.8884397</v>
+        <v>2.01433568</v>
       </c>
       <c r="N17">
-        <v>7.211560300000001</v>
+        <v>7.085664320000001</v>
       </c>
       <c r="O17">
-        <v>1.225965251</v>
+        <v>1.2045629344</v>
       </c>
       <c r="P17">
-        <v>5.985595049000001</v>
+        <v>5.881101385600001</v>
       </c>
       <c r="Q17">
-        <v>29.385595049</v>
+        <v>29.2811013856</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2494771596620469</v>
+        <v>0.2515423462353751</v>
       </c>
       <c r="T17">
-        <v>0.729433060960117</v>
+        <v>0.7368291546906857</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>4.818792996143854</v>
+        <v>4.517618433884863</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.218639410837715</v>
+        <v>0.2186911359626903</v>
       </c>
       <c r="C18">
-        <v>195.945269215404</v>
+        <v>193.6400591272098</v>
       </c>
       <c r="D18">
-        <v>119.770869215404</v>
+        <v>119.7422591272098</v>
       </c>
       <c r="E18">
-        <v>28.5656</v>
+        <v>30.84220000000001</v>
       </c>
       <c r="F18">
-        <v>36.4256</v>
+        <v>38.7022</v>
       </c>
       <c r="G18">
         <v>112.6</v>
@@ -2751,45 +2751,45 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M18">
-        <v>2.01433568</v>
+        <v>2.23698716</v>
       </c>
       <c r="N18">
-        <v>7.085664320000001</v>
+        <v>6.863012840000001</v>
       </c>
       <c r="O18">
-        <v>1.2045629344</v>
+        <v>1.1667121828</v>
       </c>
       <c r="P18">
-        <v>5.881101385600001</v>
+        <v>5.696300657200001</v>
       </c>
       <c r="Q18">
-        <v>29.2811013856</v>
+        <v>29.0963006572</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2515423462353751</v>
+        <v>0.2536572963405908</v>
       </c>
       <c r="T18">
-        <v>0.7368291546906857</v>
+        <v>0.7444034675472923</v>
       </c>
       <c r="U18">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V18">
         <v>0.17</v>
       </c>
       <c r="W18">
-        <v>0.045899</v>
+        <v>0.047974</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.517618433884863</v>
+        <v>4.067971494302185</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.2186911359626903</v>
+        <v>0.2189337610876655</v>
       </c>
       <c r="C19">
-        <v>193.6400591272098</v>
+        <v>191.2294410686032</v>
       </c>
       <c r="D19">
-        <v>119.7422591272098</v>
+        <v>119.6082410686032</v>
       </c>
       <c r="E19">
-        <v>30.84220000000001</v>
+        <v>33.11880000000001</v>
       </c>
       <c r="F19">
-        <v>38.7022</v>
+        <v>40.97880000000001</v>
       </c>
       <c r="G19">
         <v>112.6</v>
@@ -2833,45 +2833,45 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M19">
-        <v>2.23698716</v>
+        <v>2.51200044</v>
       </c>
       <c r="N19">
-        <v>6.863012840000001</v>
+        <v>6.587999560000001</v>
       </c>
       <c r="O19">
-        <v>1.1667121828</v>
+        <v>1.1199599252</v>
       </c>
       <c r="P19">
-        <v>5.696300657200001</v>
+        <v>5.4680396348</v>
       </c>
       <c r="Q19">
-        <v>29.0963006572</v>
+        <v>28.8680396348</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2536572963405908</v>
+        <v>0.255823830594714</v>
       </c>
       <c r="T19">
-        <v>0.7444034675472923</v>
+        <v>0.7521625197418648</v>
       </c>
       <c r="U19">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V19">
         <v>0.17</v>
       </c>
       <c r="W19">
-        <v>0.047974</v>
+        <v>0.050879</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.067971494302185</v>
+        <v>3.622610830434409</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.2189337610876655</v>
+        <v>0.2191240962126407</v>
       </c>
       <c r="C20">
-        <v>191.2294410686032</v>
+        <v>188.8479160630294</v>
       </c>
       <c r="D20">
-        <v>119.6082410686032</v>
+        <v>119.5033160630294</v>
       </c>
       <c r="E20">
-        <v>33.1188</v>
+        <v>35.39540000000001</v>
       </c>
       <c r="F20">
-        <v>40.9788</v>
+        <v>43.25540000000001</v>
       </c>
       <c r="G20">
         <v>112.6</v>
@@ -2915,45 +2915,45 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M20">
-        <v>2.51200044</v>
+        <v>2.772671140000001</v>
       </c>
       <c r="N20">
-        <v>6.587999560000002</v>
+        <v>6.327328860000001</v>
       </c>
       <c r="O20">
-        <v>1.1199599252</v>
+        <v>1.0756459062</v>
       </c>
       <c r="P20">
-        <v>5.468039634800002</v>
+        <v>5.2516829538</v>
       </c>
       <c r="Q20">
-        <v>28.8680396348</v>
+        <v>28.6516829538</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.255823830594714</v>
+        <v>0.2580438595217787</v>
       </c>
       <c r="T20">
-        <v>0.7521625197418648</v>
+        <v>0.7601131534721058</v>
       </c>
       <c r="U20">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V20">
         <v>0.17</v>
       </c>
       <c r="W20">
-        <v>0.050879</v>
+        <v>0.053203</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>3.62261083043441</v>
+        <v>3.282033656541035</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.2191240962126407</v>
+        <v>0.2188961113376159</v>
       </c>
       <c r="C21">
-        <v>188.8479160630294</v>
+        <v>186.6970178723437</v>
       </c>
       <c r="D21">
-        <v>119.5033160630294</v>
+        <v>119.6290178723437</v>
       </c>
       <c r="E21">
-        <v>35.39540000000001</v>
+        <v>37.67200000000001</v>
       </c>
       <c r="F21">
-        <v>43.25540000000001</v>
+        <v>45.53200000000001</v>
       </c>
       <c r="G21">
         <v>112.6</v>
@@ -2997,28 +2997,28 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M21">
-        <v>2.772671140000001</v>
+        <v>2.918601200000001</v>
       </c>
       <c r="N21">
-        <v>6.327328860000001</v>
+        <v>6.1813988</v>
       </c>
       <c r="O21">
-        <v>1.0756459062</v>
+        <v>1.050837796</v>
       </c>
       <c r="P21">
-        <v>5.2516829538</v>
+        <v>5.130561004</v>
       </c>
       <c r="Q21">
-        <v>28.6516829538</v>
+        <v>28.530561004</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2580438595217787</v>
+        <v>0.2603193891720199</v>
       </c>
       <c r="T21">
-        <v>0.7601131534721058</v>
+        <v>0.7682625530456029</v>
       </c>
       <c r="U21">
         <v>0.0641</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.282033656541035</v>
+        <v>3.117931973713983</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.2188961113376159</v>
+        <v>0.2200276664625911</v>
       </c>
       <c r="C22">
-        <v>186.6970178723437</v>
+        <v>183.7991107198487</v>
       </c>
       <c r="D22">
-        <v>119.6290178723437</v>
+        <v>119.0077107198487</v>
       </c>
       <c r="E22">
-        <v>37.67200000000001</v>
+        <v>39.94860000000001</v>
       </c>
       <c r="F22">
-        <v>45.53200000000001</v>
+        <v>47.80860000000001</v>
       </c>
       <c r="G22">
         <v>112.6</v>
@@ -3079,45 +3079,45 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M22">
-        <v>2.918601200000001</v>
+        <v>3.437438340000001</v>
       </c>
       <c r="N22">
-        <v>6.1813988</v>
+        <v>5.66256166</v>
       </c>
       <c r="O22">
-        <v>1.050837796</v>
+        <v>0.9626354822000001</v>
       </c>
       <c r="P22">
-        <v>5.130561004</v>
+        <v>4.6999261778</v>
       </c>
       <c r="Q22">
-        <v>28.530561004</v>
+        <v>28.0999261778</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2603193891720199</v>
+        <v>0.2626525271678369</v>
       </c>
       <c r="T22">
-        <v>0.7682625530456029</v>
+        <v>0.776618266532353</v>
       </c>
       <c r="U22">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V22">
         <v>0.17</v>
       </c>
       <c r="W22">
-        <v>0.053203</v>
+        <v>0.059677</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.117931973713983</v>
+        <v>2.647320213458723</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2200276664625911</v>
+        <v>0.2198644215875664</v>
       </c>
       <c r="C23">
-        <v>183.7991107198487</v>
+        <v>181.6117455248698</v>
       </c>
       <c r="D23">
-        <v>119.0077107198487</v>
+        <v>119.0969455248698</v>
       </c>
       <c r="E23">
-        <v>39.94860000000001</v>
+        <v>42.22520000000001</v>
       </c>
       <c r="F23">
-        <v>47.80860000000001</v>
+        <v>50.08520000000001</v>
       </c>
       <c r="G23">
         <v>112.6</v>
@@ -3161,28 +3161,28 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M23">
-        <v>3.437438340000001</v>
+        <v>3.601125880000001</v>
       </c>
       <c r="N23">
-        <v>5.662561660000001</v>
+        <v>5.49887412</v>
       </c>
       <c r="O23">
-        <v>0.9626354822000002</v>
+        <v>0.9348086004</v>
       </c>
       <c r="P23">
-        <v>4.6999261778</v>
+        <v>4.5640655196</v>
       </c>
       <c r="Q23">
-        <v>28.0999261778</v>
+        <v>27.9640655196</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2626525271678369</v>
+        <v>0.2650454892148287</v>
       </c>
       <c r="T23">
-        <v>0.776618266532353</v>
+        <v>0.785188229082866</v>
       </c>
       <c r="U23">
         <v>0.07190000000000001</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.647320213458723</v>
+        <v>2.526987476483327</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.2198644215875664</v>
+        <v>0.2204456867125416</v>
       </c>
       <c r="C24">
-        <v>181.6117455248698</v>
+        <v>179.0180161017242</v>
       </c>
       <c r="D24">
-        <v>119.0969455248698</v>
+        <v>118.7798161017243</v>
       </c>
       <c r="E24">
-        <v>42.22520000000001</v>
+        <v>44.50180000000001</v>
       </c>
       <c r="F24">
-        <v>50.08520000000001</v>
+        <v>52.36180000000001</v>
       </c>
       <c r="G24">
         <v>112.6</v>
@@ -3243,45 +3243,45 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M24">
-        <v>3.601125880000001</v>
+        <v>3.969024440000001</v>
       </c>
       <c r="N24">
-        <v>5.49887412</v>
+        <v>5.13097556</v>
       </c>
       <c r="O24">
-        <v>0.9348086004</v>
+        <v>0.8722658452000002</v>
       </c>
       <c r="P24">
-        <v>4.5640655196</v>
+        <v>4.2587097148</v>
       </c>
       <c r="Q24">
-        <v>27.9640655196</v>
+        <v>27.6587097148</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2650454892148287</v>
+        <v>0.2675006061201838</v>
       </c>
       <c r="T24">
-        <v>0.785188229082866</v>
+        <v>0.7939807880632624</v>
       </c>
       <c r="U24">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V24">
         <v>0.17</v>
       </c>
       <c r="W24">
-        <v>0.059677</v>
+        <v>0.062914</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.526987476483327</v>
+        <v>2.292754841287901</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2204456867125416</v>
+        <v>0.2203148118375168</v>
       </c>
       <c r="C25">
-        <v>179.0180161017242</v>
+        <v>176.812672034721</v>
       </c>
       <c r="D25">
-        <v>118.7798161017243</v>
+        <v>118.851072034721</v>
       </c>
       <c r="E25">
-        <v>44.50180000000001</v>
+        <v>46.77840000000001</v>
       </c>
       <c r="F25">
-        <v>52.36180000000001</v>
+        <v>54.63840000000001</v>
       </c>
       <c r="G25">
         <v>112.6</v>
@@ -3325,28 +3325,28 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M25">
-        <v>3.969024440000001</v>
+        <v>4.141590720000001</v>
       </c>
       <c r="N25">
-        <v>5.13097556</v>
+        <v>4.958409280000001</v>
       </c>
       <c r="O25">
-        <v>0.8722658452000002</v>
+        <v>0.8429295776000002</v>
       </c>
       <c r="P25">
-        <v>4.2587097148</v>
+        <v>4.1154797024</v>
       </c>
       <c r="Q25">
-        <v>27.6587097148</v>
+        <v>27.5154797024</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2675006061201838</v>
+        <v>0.2700203313651536</v>
       </c>
       <c r="T25">
-        <v>0.7939807880632624</v>
+        <v>0.8030047301747218</v>
       </c>
       <c r="U25">
         <v>0.07580000000000001</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.292754841287901</v>
+        <v>2.197223389567572</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2203148118375168</v>
+        <v>0.220183936962492</v>
       </c>
       <c r="C26">
-        <v>176.812672034721</v>
+        <v>174.6074135118096</v>
       </c>
       <c r="D26">
-        <v>118.851072034721</v>
+        <v>118.9224135118096</v>
       </c>
       <c r="E26">
-        <v>46.7784</v>
+        <v>49.05500000000001</v>
       </c>
       <c r="F26">
-        <v>54.6384</v>
+        <v>56.91500000000001</v>
       </c>
       <c r="G26">
         <v>112.6</v>
@@ -3407,28 +3407,28 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M26">
-        <v>4.141590720000001</v>
+        <v>4.314157000000001</v>
       </c>
       <c r="N26">
-        <v>4.958409280000001</v>
+        <v>4.785843000000001</v>
       </c>
       <c r="O26">
-        <v>0.8429295776000002</v>
+        <v>0.8135933100000002</v>
       </c>
       <c r="P26">
-        <v>4.1154797024</v>
+        <v>3.97224969</v>
       </c>
       <c r="Q26">
-        <v>27.5154797024</v>
+        <v>27.37224969</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2700203313651536</v>
+        <v>0.2726072492833226</v>
       </c>
       <c r="T26">
-        <v>0.8030047301747218</v>
+        <v>0.812269310742487</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.197223389567572</v>
+        <v>2.109334453984869</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.220183936962492</v>
+        <v>0.2200530620874672</v>
       </c>
       <c r="C27">
-        <v>174.6074135118096</v>
+        <v>172.4022406871285</v>
       </c>
       <c r="D27">
-        <v>118.9224135118096</v>
+        <v>118.9938406871285</v>
       </c>
       <c r="E27">
-        <v>49.05500000000001</v>
+        <v>51.33160000000001</v>
       </c>
       <c r="F27">
-        <v>56.91500000000001</v>
+        <v>59.19160000000001</v>
       </c>
       <c r="G27">
         <v>112.6</v>
@@ -3489,28 +3489,28 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M27">
-        <v>4.314157000000001</v>
+        <v>4.486723280000001</v>
       </c>
       <c r="N27">
-        <v>4.785843000000001</v>
+        <v>4.61327672</v>
       </c>
       <c r="O27">
-        <v>0.8135933100000002</v>
+        <v>0.7842570424</v>
       </c>
       <c r="P27">
-        <v>3.97224969</v>
+        <v>3.8290196776</v>
       </c>
       <c r="Q27">
-        <v>27.37224969</v>
+        <v>27.2290196776</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2726072492833226</v>
+        <v>0.2752640839019827</v>
       </c>
       <c r="T27">
-        <v>0.812269310742487</v>
+        <v>0.8217842853796511</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.109334453984869</v>
+        <v>2.028206205754681</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2200530620874672</v>
+        <v>0.2231044072124424</v>
       </c>
       <c r="C28">
-        <v>172.4022406871285</v>
+        <v>168.482329296294</v>
       </c>
       <c r="D28">
-        <v>118.9938406871285</v>
+        <v>117.350529296294</v>
       </c>
       <c r="E28">
-        <v>51.33160000000001</v>
+        <v>53.60820000000001</v>
       </c>
       <c r="F28">
-        <v>59.19160000000001</v>
+        <v>61.46820000000001</v>
       </c>
       <c r="G28">
         <v>112.6</v>
@@ -3571,45 +3571,45 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M28">
-        <v>4.486723280000001</v>
+        <v>5.532138000000001</v>
       </c>
       <c r="N28">
-        <v>4.61327672</v>
+        <v>3.567862000000001</v>
       </c>
       <c r="O28">
-        <v>0.7842570424</v>
+        <v>0.6065365400000001</v>
       </c>
       <c r="P28">
-        <v>3.8290196776</v>
+        <v>2.961325460000001</v>
       </c>
       <c r="Q28">
-        <v>27.2290196776</v>
+        <v>26.36132546</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2752640839019827</v>
+        <v>0.2779937085101951</v>
       </c>
       <c r="T28">
-        <v>0.8217842853796511</v>
+        <v>0.8315599442534499</v>
       </c>
       <c r="U28">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V28">
         <v>0.17</v>
       </c>
       <c r="W28">
-        <v>0.062914</v>
+        <v>0.07469999999999999</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.028206205754681</v>
+        <v>1.644933658560217</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2231044072124424</v>
+        <v>0.2230913923374176</v>
       </c>
       <c r="C29">
-        <v>168.482329296294</v>
+        <v>166.2126421073879</v>
       </c>
       <c r="D29">
-        <v>117.350529296294</v>
+        <v>117.3574421073879</v>
       </c>
       <c r="E29">
-        <v>53.60820000000001</v>
+        <v>55.88480000000001</v>
       </c>
       <c r="F29">
-        <v>61.46820000000001</v>
+        <v>63.74480000000001</v>
       </c>
       <c r="G29">
         <v>112.6</v>
@@ -3653,28 +3653,28 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M29">
-        <v>5.532138000000001</v>
+        <v>5.737032000000001</v>
       </c>
       <c r="N29">
-        <v>3.567862000000001</v>
+        <v>3.362968</v>
       </c>
       <c r="O29">
-        <v>0.6065365400000001</v>
+        <v>0.5717045600000001</v>
       </c>
       <c r="P29">
-        <v>2.961325460000001</v>
+        <v>2.79126344</v>
       </c>
       <c r="Q29">
-        <v>26.36132546</v>
+        <v>26.19126344</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2779937085101951</v>
+        <v>0.2807991560241911</v>
       </c>
       <c r="T29">
-        <v>0.8315599442534499</v>
+        <v>0.8416071492070764</v>
       </c>
       <c r="U29">
         <v>0.09</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>1.644933658560217</v>
+        <v>1.586186027897352</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2230913923374176</v>
+        <v>0.2230783774623928</v>
       </c>
       <c r="C30">
-        <v>166.2126421073879</v>
+        <v>163.9429557329608</v>
       </c>
       <c r="D30">
-        <v>117.3574421073879</v>
+        <v>117.3643557329608</v>
       </c>
       <c r="E30">
-        <v>55.88480000000001</v>
+        <v>58.16140000000001</v>
       </c>
       <c r="F30">
-        <v>63.74480000000001</v>
+        <v>66.02140000000001</v>
       </c>
       <c r="G30">
         <v>112.6</v>
@@ -3735,28 +3735,28 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M30">
-        <v>5.737032000000001</v>
+        <v>5.941926000000001</v>
       </c>
       <c r="N30">
-        <v>3.362968</v>
+        <v>3.158074</v>
       </c>
       <c r="O30">
-        <v>0.5717045600000001</v>
+        <v>0.53687258</v>
       </c>
       <c r="P30">
-        <v>2.79126344</v>
+        <v>2.62120142</v>
       </c>
       <c r="Q30">
-        <v>26.19126344</v>
+        <v>26.02120142</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2807991560241911</v>
+        <v>0.2836836302287223</v>
       </c>
       <c r="T30">
-        <v>0.8416071492070764</v>
+        <v>0.8519373740185516</v>
       </c>
       <c r="U30">
         <v>0.09</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.586186027897352</v>
+        <v>1.531489957969857</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2230783774623928</v>
+        <v>0.2387370833104486</v>
       </c>
       <c r="C31">
-        <v>163.9429557329609</v>
+        <v>153.8983894656246</v>
       </c>
       <c r="D31">
-        <v>117.3643557329609</v>
+        <v>109.5963894656246</v>
       </c>
       <c r="E31">
-        <v>58.1614</v>
+        <v>60.438</v>
       </c>
       <c r="F31">
-        <v>66.0214</v>
+        <v>68.298</v>
       </c>
       <c r="G31">
         <v>112.6</v>
@@ -3817,45 +3817,45 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M31">
-        <v>5.941926</v>
+        <v>10.0261464</v>
       </c>
       <c r="N31">
-        <v>3.158074000000002</v>
+        <v>-0.9261464000000004</v>
       </c>
       <c r="O31">
-        <v>0.5368725800000004</v>
+        <v>-0.1574448880000001</v>
       </c>
       <c r="P31">
-        <v>2.621201420000002</v>
+        <v>-0.7687015120000003</v>
       </c>
       <c r="Q31">
-        <v>26.02120142</v>
+        <v>22.631298488</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2836836302287223</v>
+        <v>0.2878461489342298</v>
       </c>
       <c r="T31">
-        <v>0.8519373740185515</v>
+        <v>0.8668446850086501</v>
       </c>
       <c r="U31">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V31">
-        <v>0.17</v>
+        <v>0.1542965700161729</v>
       </c>
       <c r="W31">
-        <v>0.07469999999999999</v>
+        <v>0.1241492635216258</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y31">
-        <v>1.531489957969857</v>
+        <v>0.907626882448076</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2387370833104486</v>
+        <v>0.2397470833104486</v>
       </c>
       <c r="C32">
-        <v>153.8983894656246</v>
+        <v>151.1559001343608</v>
       </c>
       <c r="D32">
-        <v>109.5963894656246</v>
+        <v>109.1305001343608</v>
       </c>
       <c r="E32">
-        <v>60.438</v>
+        <v>62.7146</v>
       </c>
       <c r="F32">
-        <v>68.298</v>
+        <v>70.5746</v>
       </c>
       <c r="G32">
         <v>112.6</v>
@@ -3899,37 +3899,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M32">
-        <v>10.0261464</v>
+        <v>10.36035128</v>
       </c>
       <c r="N32">
-        <v>-0.9261464000000004</v>
+        <v>-1.26035128</v>
       </c>
       <c r="O32">
-        <v>-0.1574448880000001</v>
+        <v>-0.2142597176</v>
       </c>
       <c r="P32">
-        <v>-0.7687015120000003</v>
+        <v>-1.0460915624</v>
       </c>
       <c r="Q32">
-        <v>22.631298488</v>
+        <v>22.3539084376</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2878461489342298</v>
+        <v>0.2913540641361752</v>
       </c>
       <c r="T32">
-        <v>0.8668446850086501</v>
+        <v>0.8794076514580508</v>
       </c>
       <c r="U32">
         <v>0.1468</v>
       </c>
       <c r="V32">
-        <v>0.1542965700161729</v>
+        <v>0.1493192613059738</v>
       </c>
       <c r="W32">
-        <v>0.1241492635216258</v>
+        <v>0.1248799324402831</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.907626882448076</v>
+        <v>0.8783485959174929</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2397470833104486</v>
+        <v>0.2407570833104486</v>
       </c>
       <c r="C33">
-        <v>151.1559001343608</v>
+        <v>148.4173549858153</v>
       </c>
       <c r="D33">
-        <v>109.1305001343608</v>
+        <v>108.6685549858153</v>
       </c>
       <c r="E33">
-        <v>62.7146</v>
+        <v>64.99120000000001</v>
       </c>
       <c r="F33">
-        <v>70.5746</v>
+        <v>72.85120000000001</v>
       </c>
       <c r="G33">
         <v>112.6</v>
@@ -3981,37 +3981,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M33">
-        <v>10.36035128</v>
+        <v>10.69455616</v>
       </c>
       <c r="N33">
-        <v>-1.26035128</v>
+        <v>-1.59455616</v>
       </c>
       <c r="O33">
-        <v>-0.2142597176</v>
+        <v>-0.2710745472</v>
       </c>
       <c r="P33">
-        <v>-1.0460915624</v>
+        <v>-1.3234816128</v>
       </c>
       <c r="Q33">
-        <v>22.3539084376</v>
+        <v>22.0765183872</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2913540641361752</v>
+        <v>0.2949651533146483</v>
       </c>
       <c r="T33">
-        <v>0.8794076514580508</v>
+        <v>0.8923401169206693</v>
       </c>
       <c r="U33">
         <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.1493192613059738</v>
+        <v>0.1446530343901621</v>
       </c>
       <c r="W33">
-        <v>0.1248799324402831</v>
+        <v>0.1255649345515242</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.8783485959174929</v>
+        <v>0.8509002022950712</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2407570833104486</v>
+        <v>0.2417670833104487</v>
       </c>
       <c r="C34">
-        <v>148.4173549858153</v>
+        <v>145.682704144395</v>
       </c>
       <c r="D34">
-        <v>108.6685549858153</v>
+        <v>108.210504144395</v>
       </c>
       <c r="E34">
-        <v>64.99120000000001</v>
+        <v>67.26780000000001</v>
       </c>
       <c r="F34">
-        <v>72.85120000000001</v>
+        <v>75.12780000000001</v>
       </c>
       <c r="G34">
         <v>112.6</v>
@@ -4063,37 +4063,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M34">
-        <v>10.69455616</v>
+        <v>11.02876104</v>
       </c>
       <c r="N34">
-        <v>-1.59455616</v>
+        <v>-1.928761040000001</v>
       </c>
       <c r="O34">
-        <v>-0.2710745472</v>
+        <v>-0.3278893768000002</v>
       </c>
       <c r="P34">
-        <v>-1.3234816128</v>
+        <v>-1.600871663200001</v>
       </c>
       <c r="Q34">
-        <v>22.0765183872</v>
+        <v>21.7991283368</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2949651533146483</v>
+        <v>0.2986840361999417</v>
       </c>
       <c r="T34">
-        <v>0.8923401169206693</v>
+        <v>0.9056586261284405</v>
       </c>
       <c r="U34">
         <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.1446530343901621</v>
+        <v>0.1402696091056117</v>
       </c>
       <c r="W34">
-        <v>0.1255649345515242</v>
+        <v>0.1262084213832962</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8509002022950712</v>
+        <v>0.825115347680069</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.2417670833104487</v>
+        <v>0.2427770833104486</v>
       </c>
       <c r="C35">
-        <v>145.682704144395</v>
+        <v>142.9518985719031</v>
       </c>
       <c r="D35">
-        <v>108.210504144395</v>
+        <v>107.7562985719031</v>
       </c>
       <c r="E35">
-        <v>67.26780000000001</v>
+        <v>69.54440000000001</v>
       </c>
       <c r="F35">
-        <v>75.12780000000001</v>
+        <v>77.40440000000001</v>
       </c>
       <c r="G35">
         <v>112.6</v>
@@ -4145,37 +4145,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M35">
-        <v>11.02876104</v>
+        <v>11.36296592</v>
       </c>
       <c r="N35">
-        <v>-1.928761040000001</v>
+        <v>-2.262965920000001</v>
       </c>
       <c r="O35">
-        <v>-0.3278893768000002</v>
+        <v>-0.3847042064000002</v>
       </c>
       <c r="P35">
-        <v>-1.600871663200001</v>
+        <v>-1.878261713600001</v>
       </c>
       <c r="Q35">
-        <v>21.7991283368</v>
+        <v>21.5217382864</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2986840361999417</v>
+        <v>0.3025156125060013</v>
       </c>
       <c r="T35">
-        <v>0.9056586261284405</v>
+        <v>0.9193807265243259</v>
       </c>
       <c r="U35">
         <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.1402696091056117</v>
+        <v>0.1361440323672114</v>
       </c>
       <c r="W35">
-        <v>0.1262084213832962</v>
+        <v>0.1268140560484934</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.825115347680069</v>
+        <v>0.8008472492188905</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.2427770833104486</v>
+        <v>0.2648985835472222</v>
       </c>
       <c r="C36">
-        <v>142.9518985719031</v>
+        <v>131.6028918966851</v>
       </c>
       <c r="D36">
-        <v>107.7562985719031</v>
+        <v>98.6838918966851</v>
       </c>
       <c r="E36">
-        <v>69.54440000000001</v>
+        <v>71.82100000000001</v>
       </c>
       <c r="F36">
-        <v>77.40440000000001</v>
+        <v>79.68100000000001</v>
       </c>
       <c r="G36">
         <v>112.6</v>
@@ -4227,45 +4227,45 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M36">
-        <v>11.36296592</v>
+        <v>15.9999448</v>
       </c>
       <c r="N36">
-        <v>-2.262965920000001</v>
+        <v>-6.899944800000002</v>
       </c>
       <c r="O36">
-        <v>-0.3847042064000002</v>
+        <v>-1.172990616</v>
       </c>
       <c r="P36">
-        <v>-1.878261713600001</v>
+        <v>-5.726954184000002</v>
       </c>
       <c r="Q36">
-        <v>21.5217382864</v>
+        <v>17.673045816</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.3025156125060013</v>
+        <v>0.3098673915242069</v>
       </c>
       <c r="T36">
-        <v>0.9193807265243259</v>
+        <v>0.9457097988741666</v>
       </c>
       <c r="U36">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.1361440323672114</v>
+        <v>0.09668783357302582</v>
       </c>
       <c r="W36">
-        <v>0.1268140560484934</v>
+        <v>0.1813850830185364</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y36">
-        <v>0.8008472492188905</v>
+        <v>0.5687519621942696</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2648985835472222</v>
+        <v>0.2664485835472222</v>
       </c>
       <c r="C37">
-        <v>131.6028918966851</v>
+        <v>128.7475449009765</v>
       </c>
       <c r="D37">
-        <v>98.6838918966851</v>
+        <v>98.10514490097648</v>
       </c>
       <c r="E37">
-        <v>71.82100000000001</v>
+        <v>74.09760000000001</v>
       </c>
       <c r="F37">
-        <v>79.68100000000001</v>
+        <v>81.95760000000001</v>
       </c>
       <c r="G37">
         <v>112.6</v>
@@ -4309,37 +4309,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M37">
-        <v>15.9999448</v>
+        <v>16.45708608</v>
       </c>
       <c r="N37">
-        <v>-6.899944800000002</v>
+        <v>-7.357086080000002</v>
       </c>
       <c r="O37">
-        <v>-1.172990616</v>
+        <v>-1.250704633600001</v>
       </c>
       <c r="P37">
-        <v>-5.726954184000002</v>
+        <v>-6.106381446400001</v>
       </c>
       <c r="Q37">
-        <v>17.673045816</v>
+        <v>17.2936185536</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.3098673915242069</v>
+        <v>0.3139934445167727</v>
       </c>
       <c r="T37">
-        <v>0.9457097988741666</v>
+        <v>0.9604865144815754</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.09668783357302582</v>
+        <v>0.09400206041821955</v>
       </c>
       <c r="W37">
-        <v>0.1813850830185364</v>
+        <v>0.1819243862680215</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.5687519621942696</v>
+        <v>0.552953296577762</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2664485835472223</v>
+        <v>0.2679985835472223</v>
       </c>
       <c r="C38">
-        <v>128.7475449009764</v>
+        <v>125.898946629436</v>
       </c>
       <c r="D38">
-        <v>98.10514490097647</v>
+        <v>97.53314662943598</v>
       </c>
       <c r="E38">
-        <v>74.0976</v>
+        <v>76.3742</v>
       </c>
       <c r="F38">
-        <v>81.9576</v>
+        <v>84.2342</v>
       </c>
       <c r="G38">
         <v>112.6</v>
@@ -4391,37 +4391,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M38">
-        <v>16.45708608</v>
+        <v>16.91422736</v>
       </c>
       <c r="N38">
-        <v>-7.357086079999998</v>
+        <v>-7.81422736</v>
       </c>
       <c r="O38">
-        <v>-1.2507046336</v>
+        <v>-1.3284186512</v>
       </c>
       <c r="P38">
-        <v>-6.106381446399999</v>
+        <v>-6.4858087088</v>
       </c>
       <c r="Q38">
-        <v>17.2936185536</v>
+        <v>16.9141912912</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.3139934445167727</v>
+        <v>0.3182504833186262</v>
       </c>
       <c r="T38">
-        <v>0.9604865144815754</v>
+        <v>0.9757323321717591</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.09400206041821957</v>
+        <v>0.09146146419070013</v>
       </c>
       <c r="W38">
-        <v>0.1819243862680215</v>
+        <v>0.1824345379905074</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.5529532965777622</v>
+        <v>0.5380086128864712</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2679985835472223</v>
+        <v>0.2695485835472222</v>
       </c>
       <c r="C39">
-        <v>125.898946629436</v>
+        <v>123.0569797217985</v>
       </c>
       <c r="D39">
-        <v>97.53314662943598</v>
+        <v>96.96777972179856</v>
       </c>
       <c r="E39">
-        <v>76.3742</v>
+        <v>78.65080000000002</v>
       </c>
       <c r="F39">
-        <v>84.2342</v>
+        <v>86.51080000000002</v>
       </c>
       <c r="G39">
         <v>112.6</v>
@@ -4473,37 +4473,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M39">
-        <v>16.91422736</v>
+        <v>17.37136864</v>
       </c>
       <c r="N39">
-        <v>-7.81422736</v>
+        <v>-8.271368640000002</v>
       </c>
       <c r="O39">
-        <v>-1.3284186512</v>
+        <v>-1.4061326688</v>
       </c>
       <c r="P39">
-        <v>-6.4858087088</v>
+        <v>-6.865235971200002</v>
       </c>
       <c r="Q39">
-        <v>16.9141912912</v>
+        <v>16.5347640288</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.3182504833186262</v>
+        <v>0.3226448459527976</v>
       </c>
       <c r="T39">
-        <v>0.9757323321717591</v>
+        <v>0.9914699504325939</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.09146146419070013</v>
+        <v>0.08905458355410274</v>
       </c>
       <c r="W39">
-        <v>0.1824345379905074</v>
+        <v>0.1829178396223362</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5380086128864712</v>
+        <v>0.523850491494722</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2695485835472222</v>
+        <v>0.2710985835472223</v>
       </c>
       <c r="C40">
-        <v>123.0569797217985</v>
+        <v>120.2215295233084</v>
       </c>
       <c r="D40">
-        <v>96.96777972179856</v>
+        <v>96.4089295233084</v>
       </c>
       <c r="E40">
-        <v>78.65080000000002</v>
+        <v>80.92740000000002</v>
       </c>
       <c r="F40">
-        <v>86.51080000000002</v>
+        <v>88.78740000000002</v>
       </c>
       <c r="G40">
         <v>112.6</v>
@@ -4555,37 +4555,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M40">
-        <v>17.37136864</v>
+        <v>17.82850992000001</v>
       </c>
       <c r="N40">
-        <v>-8.271368640000002</v>
+        <v>-8.728509920000004</v>
       </c>
       <c r="O40">
-        <v>-1.4061326688</v>
+        <v>-1.483846686400001</v>
       </c>
       <c r="P40">
-        <v>-6.865235971200002</v>
+        <v>-7.244663233600003</v>
       </c>
       <c r="Q40">
-        <v>16.5347640288</v>
+        <v>16.15533676639999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.3226448459527976</v>
+        <v>0.3271832860503844</v>
       </c>
       <c r="T40">
-        <v>0.9914699504325939</v>
+        <v>1.007723556177391</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.08905458355410274</v>
+        <v>0.08677113269374111</v>
       </c>
       <c r="W40">
-        <v>0.1829178396223362</v>
+        <v>0.1833763565550968</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.523850491494722</v>
+        <v>0.5104184276102419</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2710985835472223</v>
+        <v>0.2875409506047211</v>
       </c>
       <c r="C41">
-        <v>120.2215295233084</v>
+        <v>112.3904086297643</v>
       </c>
       <c r="D41">
-        <v>96.4089295233084</v>
+        <v>90.85440862976435</v>
       </c>
       <c r="E41">
-        <v>80.92740000000002</v>
+        <v>83.20400000000002</v>
       </c>
       <c r="F41">
-        <v>88.78740000000002</v>
+        <v>91.06400000000002</v>
       </c>
       <c r="G41">
         <v>112.6</v>
@@ -4637,45 +4637,45 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M41">
-        <v>17.82850992000001</v>
+        <v>21.47289120000001</v>
       </c>
       <c r="N41">
-        <v>-8.728509920000004</v>
+        <v>-12.37289120000001</v>
       </c>
       <c r="O41">
-        <v>-1.483846686400001</v>
+        <v>-2.103391504000001</v>
       </c>
       <c r="P41">
-        <v>-7.244663233600003</v>
+        <v>-10.269499696</v>
       </c>
       <c r="Q41">
-        <v>16.15533676639999</v>
+        <v>13.13050030399999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.3271832860503844</v>
+        <v>0.3333602859137221</v>
       </c>
       <c r="T41">
-        <v>1.007723556177391</v>
+        <v>1.029845368585521</v>
       </c>
       <c r="U41">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.08677113269374111</v>
+        <v>0.07204432722129193</v>
       </c>
       <c r="W41">
-        <v>0.1833763565550968</v>
+        <v>0.2188119476412194</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y41">
-        <v>0.5104184276102419</v>
+        <v>0.4237901601252466</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2875409506047211</v>
+        <v>0.289440950604721</v>
       </c>
       <c r="C42">
-        <v>112.3904086297643</v>
+        <v>109.5129354367813</v>
       </c>
       <c r="D42">
-        <v>90.85440862976435</v>
+        <v>90.25353543678131</v>
       </c>
       <c r="E42">
-        <v>83.20400000000002</v>
+        <v>85.48060000000002</v>
       </c>
       <c r="F42">
-        <v>91.06400000000002</v>
+        <v>93.34060000000002</v>
       </c>
       <c r="G42">
         <v>112.6</v>
@@ -4719,37 +4719,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M42">
-        <v>21.47289120000001</v>
+        <v>22.00971348000001</v>
       </c>
       <c r="N42">
-        <v>-12.37289120000001</v>
+        <v>-12.90971348</v>
       </c>
       <c r="O42">
-        <v>-2.103391504000001</v>
+        <v>-2.194651291600001</v>
       </c>
       <c r="P42">
-        <v>-10.269499696</v>
+        <v>-10.7150621884</v>
       </c>
       <c r="Q42">
-        <v>13.13050030399999</v>
+        <v>12.6849378116</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.3333602859137221</v>
+        <v>0.3382341890648022</v>
       </c>
       <c r="T42">
-        <v>1.029845368585521</v>
+        <v>1.047300374832733</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.07204432722129193</v>
+        <v>0.07028714850857749</v>
       </c>
       <c r="W42">
-        <v>0.2188119476412194</v>
+        <v>0.2192262903816774</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.4237901601252466</v>
+        <v>0.4134538147563381</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.289440950604721</v>
+        <v>0.291340950604721</v>
       </c>
       <c r="C43">
-        <v>109.5129354367813</v>
+        <v>106.6433578751243</v>
       </c>
       <c r="D43">
-        <v>90.25353543678131</v>
+        <v>89.66055787512428</v>
       </c>
       <c r="E43">
-        <v>85.48060000000002</v>
+        <v>87.75720000000003</v>
       </c>
       <c r="F43">
-        <v>93.34060000000002</v>
+        <v>95.61720000000003</v>
       </c>
       <c r="G43">
         <v>112.6</v>
@@ -4801,37 +4801,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M43">
-        <v>22.00971348000001</v>
+        <v>22.54653576000001</v>
       </c>
       <c r="N43">
-        <v>-12.90971348</v>
+        <v>-13.44653576000001</v>
       </c>
       <c r="O43">
-        <v>-2.194651291600001</v>
+        <v>-2.285911079200001</v>
       </c>
       <c r="P43">
-        <v>-10.7150621884</v>
+        <v>-11.16062468080001</v>
       </c>
       <c r="Q43">
-        <v>12.6849378116</v>
+        <v>12.23937531919999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.3382341890648022</v>
+        <v>0.3432761578417815</v>
       </c>
       <c r="T43">
-        <v>1.047300374832733</v>
+        <v>1.065357277847091</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.07028714850857749</v>
+        <v>0.06861364497265897</v>
       </c>
       <c r="W43">
-        <v>0.2192262903816774</v>
+        <v>0.219620902515447</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.4134538147563381</v>
+        <v>0.4036096763097586</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.291340950604721</v>
+        <v>0.293240950604721</v>
       </c>
       <c r="C44">
-        <v>106.6433578751243</v>
+        <v>103.7815213346033</v>
       </c>
       <c r="D44">
-        <v>89.66055787512427</v>
+        <v>89.0753213346033</v>
       </c>
       <c r="E44">
-        <v>87.75720000000001</v>
+        <v>90.03380000000001</v>
       </c>
       <c r="F44">
-        <v>95.61720000000001</v>
+        <v>97.89380000000001</v>
       </c>
       <c r="G44">
         <v>112.6</v>
@@ -4883,37 +4883,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M44">
-        <v>22.54653576</v>
+        <v>23.08335804</v>
       </c>
       <c r="N44">
-        <v>-13.44653576</v>
+        <v>-13.98335804</v>
       </c>
       <c r="O44">
-        <v>-2.285911079200001</v>
+        <v>-2.377170866800001</v>
       </c>
       <c r="P44">
-        <v>-11.1606246808</v>
+        <v>-11.6061871732</v>
       </c>
       <c r="Q44">
-        <v>12.2393753192</v>
+        <v>11.7938128268</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.3432761578417815</v>
+        <v>0.3484950378039179</v>
       </c>
       <c r="T44">
-        <v>1.065357277847091</v>
+        <v>1.084047756405811</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.06861364497265898</v>
+        <v>0.06701797881050413</v>
       </c>
       <c r="W44">
-        <v>0.219620902515447</v>
+        <v>0.2199971605964831</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4036096763097587</v>
+        <v>0.3942234047676713</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.293240950604721</v>
+        <v>0.295140950604721</v>
       </c>
       <c r="C45">
-        <v>103.7815213346033</v>
+        <v>100.9272752155657</v>
       </c>
       <c r="D45">
-        <v>89.0753213346033</v>
+        <v>88.49767521556574</v>
       </c>
       <c r="E45">
-        <v>90.03380000000001</v>
+        <v>92.31040000000002</v>
       </c>
       <c r="F45">
-        <v>97.89380000000001</v>
+        <v>100.1704</v>
       </c>
       <c r="G45">
         <v>112.6</v>
@@ -4965,37 +4965,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M45">
-        <v>23.08335804</v>
+        <v>23.62018032</v>
       </c>
       <c r="N45">
-        <v>-13.98335804</v>
+        <v>-14.52018032</v>
       </c>
       <c r="O45">
-        <v>-2.377170866800001</v>
+        <v>-2.468430654400001</v>
       </c>
       <c r="P45">
-        <v>-11.6061871732</v>
+        <v>-12.0517496656</v>
       </c>
       <c r="Q45">
-        <v>11.7938128268</v>
+        <v>11.3482503344</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.3484950378039179</v>
+        <v>0.3539003063361308</v>
       </c>
       <c r="T45">
-        <v>1.084047756405811</v>
+        <v>1.103405752055915</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.06701797881050413</v>
+        <v>0.06549484292844722</v>
       </c>
       <c r="W45">
-        <v>0.2199971605964831</v>
+        <v>0.2203563160374722</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3942234047676713</v>
+        <v>0.3852637819320425</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.295140950604721</v>
+        <v>0.297040950604721</v>
       </c>
       <c r="C46">
-        <v>100.9272752155657</v>
+        <v>98.08047279969422</v>
       </c>
       <c r="D46">
-        <v>88.49767521556574</v>
+        <v>87.92747279969423</v>
       </c>
       <c r="E46">
-        <v>92.31040000000002</v>
+        <v>94.58700000000002</v>
       </c>
       <c r="F46">
-        <v>100.1704</v>
+        <v>102.447</v>
       </c>
       <c r="G46">
         <v>112.6</v>
@@ -5047,37 +5047,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M46">
-        <v>23.62018032</v>
+        <v>24.15700260000001</v>
       </c>
       <c r="N46">
-        <v>-14.52018032</v>
+        <v>-15.0570026</v>
       </c>
       <c r="O46">
-        <v>-2.468430654400001</v>
+        <v>-2.559690442000001</v>
       </c>
       <c r="P46">
-        <v>-12.0517496656</v>
+        <v>-12.497312158</v>
       </c>
       <c r="Q46">
-        <v>11.3482503344</v>
+        <v>10.902687842</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.3539003063361308</v>
+        <v>0.3595021300876969</v>
       </c>
       <c r="T46">
-        <v>1.103405752055915</v>
+        <v>1.123467674820568</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.06549484292844722</v>
+        <v>0.06403940197448171</v>
       </c>
       <c r="W46">
-        <v>0.2203563160374722</v>
+        <v>0.2206995090144172</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3852637819320425</v>
+        <v>0.3767023645557748</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.297040950604721</v>
+        <v>0.298940950604721</v>
       </c>
       <c r="C47">
-        <v>98.08047279969422</v>
+        <v>95.24097112576716</v>
       </c>
       <c r="D47">
-        <v>87.92747279969423</v>
+        <v>87.3645711257672</v>
       </c>
       <c r="E47">
-        <v>94.58700000000002</v>
+        <v>96.86360000000002</v>
       </c>
       <c r="F47">
-        <v>102.447</v>
+        <v>104.7236</v>
       </c>
       <c r="G47">
         <v>112.6</v>
@@ -5129,37 +5129,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M47">
-        <v>24.15700260000001</v>
+        <v>24.69382488</v>
       </c>
       <c r="N47">
-        <v>-15.0570026</v>
+        <v>-15.59382488</v>
       </c>
       <c r="O47">
-        <v>-2.559690442000001</v>
+        <v>-2.650950229600001</v>
       </c>
       <c r="P47">
-        <v>-12.497312158</v>
+        <v>-12.9428746504</v>
       </c>
       <c r="Q47">
-        <v>10.902687842</v>
+        <v>10.4571253496</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3595021300876969</v>
+        <v>0.3653114287930245</v>
       </c>
       <c r="T47">
-        <v>1.123467674820568</v>
+        <v>1.14427263176169</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.06403940197448171</v>
+        <v>0.06264724106199299</v>
       </c>
       <c r="W47">
-        <v>0.2206995090144172</v>
+        <v>0.2210277805575821</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3767023645557748</v>
+        <v>0.3685131827176058</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.298940950604721</v>
+        <v>0.300840950604721</v>
       </c>
       <c r="C48">
-        <v>95.24097112576716</v>
+        <v>92.4086308701615</v>
       </c>
       <c r="D48">
-        <v>87.3645711257672</v>
+        <v>86.80883087016153</v>
       </c>
       <c r="E48">
-        <v>96.86360000000002</v>
+        <v>99.14020000000002</v>
       </c>
       <c r="F48">
-        <v>104.7236</v>
+        <v>107.0002</v>
       </c>
       <c r="G48">
         <v>112.6</v>
@@ -5211,37 +5211,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M48">
-        <v>24.69382488</v>
+        <v>25.23064716000001</v>
       </c>
       <c r="N48">
-        <v>-15.59382488</v>
+        <v>-16.13064716000001</v>
       </c>
       <c r="O48">
-        <v>-2.650950229600001</v>
+        <v>-2.742210017200001</v>
       </c>
       <c r="P48">
-        <v>-12.9428746504</v>
+        <v>-13.3884371428</v>
       </c>
       <c r="Q48">
-        <v>10.4571253496</v>
+        <v>10.01156285719999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3653114287930245</v>
+        <v>0.3713399463174212</v>
       </c>
       <c r="T48">
-        <v>1.14427263176169</v>
+        <v>1.165862681417571</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.06264724106199299</v>
+        <v>0.06131432103939739</v>
       </c>
       <c r="W48">
-        <v>0.2210277805575821</v>
+        <v>0.2213420830989101</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3685131827176058</v>
+        <v>0.3606724767023375</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.300840950604721</v>
+        <v>0.302740950604721</v>
       </c>
       <c r="C49">
-        <v>92.4086308701615</v>
+        <v>89.58331623188703</v>
       </c>
       <c r="D49">
-        <v>86.80883087016153</v>
+        <v>86.26011623188704</v>
       </c>
       <c r="E49">
-        <v>99.14020000000002</v>
+        <v>101.4168</v>
       </c>
       <c r="F49">
-        <v>107.0002</v>
+        <v>109.2768</v>
       </c>
       <c r="G49">
         <v>112.6</v>
@@ -5293,37 +5293,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M49">
-        <v>25.23064716000001</v>
+        <v>25.76746944000001</v>
       </c>
       <c r="N49">
-        <v>-16.13064716000001</v>
+        <v>-16.66746944</v>
       </c>
       <c r="O49">
-        <v>-2.742210017200001</v>
+        <v>-2.833469804800001</v>
       </c>
       <c r="P49">
-        <v>-13.3884371428</v>
+        <v>-13.8339996352</v>
       </c>
       <c r="Q49">
-        <v>10.01156285719999</v>
+        <v>9.566000364799994</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3713399463174212</v>
+        <v>0.3776003299004486</v>
       </c>
       <c r="T49">
-        <v>1.165862681417571</v>
+        <v>1.188283117598678</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.06131432103939739</v>
+        <v>0.06003693935107661</v>
       </c>
       <c r="W49">
-        <v>0.2213420830989101</v>
+        <v>0.2216432897010162</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3606724767023375</v>
+        <v>0.3531584667710389</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.302740950604721</v>
+        <v>0.304640950604721</v>
       </c>
       <c r="C50">
-        <v>89.58331623188704</v>
+        <v>86.7648948219537</v>
       </c>
       <c r="D50">
-        <v>86.26011623188704</v>
+        <v>85.71829482195371</v>
       </c>
       <c r="E50">
-        <v>101.4168</v>
+        <v>103.6934</v>
       </c>
       <c r="F50">
-        <v>109.2768</v>
+        <v>111.5534</v>
       </c>
       <c r="G50">
         <v>112.6</v>
@@ -5375,37 +5375,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M50">
-        <v>25.76746944</v>
+        <v>26.30429172</v>
       </c>
       <c r="N50">
-        <v>-16.66746944</v>
+        <v>-17.20429172</v>
       </c>
       <c r="O50">
-        <v>-2.8334698048</v>
+        <v>-2.9247295924</v>
       </c>
       <c r="P50">
-        <v>-13.8339996352</v>
+        <v>-14.2795621276</v>
       </c>
       <c r="Q50">
-        <v>9.566000364799997</v>
+        <v>9.120437872399998</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.3776003299004486</v>
+        <v>0.384106218722026</v>
       </c>
       <c r="T50">
-        <v>1.188283117598678</v>
+        <v>1.211582786571201</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.06003693935107662</v>
+        <v>0.05881169569085056</v>
       </c>
       <c r="W50">
-        <v>0.2216432897010162</v>
+        <v>0.2219322021560975</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3531584667710389</v>
+        <v>0.3459511511226504</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.304640950604721</v>
+        <v>0.306540950604721</v>
       </c>
       <c r="C51">
-        <v>86.7648948219537</v>
+        <v>83.9532375568825</v>
       </c>
       <c r="D51">
-        <v>85.71829482195371</v>
+        <v>85.18323755688252</v>
       </c>
       <c r="E51">
-        <v>103.6934</v>
+        <v>105.97</v>
       </c>
       <c r="F51">
-        <v>111.5534</v>
+        <v>113.83</v>
       </c>
       <c r="G51">
         <v>112.6</v>
@@ -5457,37 +5457,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M51">
-        <v>26.30429172</v>
+        <v>26.841114</v>
       </c>
       <c r="N51">
-        <v>-17.20429172</v>
+        <v>-17.741114</v>
       </c>
       <c r="O51">
-        <v>-2.9247295924</v>
+        <v>-3.015989380000001</v>
       </c>
       <c r="P51">
-        <v>-14.2795621276</v>
+        <v>-14.72512462</v>
       </c>
       <c r="Q51">
-        <v>9.120437872399998</v>
+        <v>8.674875379999996</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.384106218722026</v>
+        <v>0.3908723430964665</v>
       </c>
       <c r="T51">
-        <v>1.211582786571201</v>
+        <v>1.235814442302625</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.05881169569085056</v>
+        <v>0.05763546177703355</v>
       </c>
       <c r="W51">
-        <v>0.2219322021560975</v>
+        <v>0.2222095581129755</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3459511511226504</v>
+        <v>0.3390321281001973</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.306540950604721</v>
+        <v>0.308440950604721</v>
       </c>
       <c r="C52">
-        <v>83.9532375568825</v>
+        <v>81.14821855617964</v>
       </c>
       <c r="D52">
-        <v>85.18323755688252</v>
+        <v>84.65481855617968</v>
       </c>
       <c r="E52">
-        <v>105.97</v>
+        <v>108.2466</v>
       </c>
       <c r="F52">
-        <v>113.83</v>
+        <v>116.1066</v>
       </c>
       <c r="G52">
         <v>112.6</v>
@@ -5539,37 +5539,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M52">
-        <v>26.841114</v>
+        <v>27.37793628</v>
       </c>
       <c r="N52">
-        <v>-17.741114</v>
+        <v>-18.27793628</v>
       </c>
       <c r="O52">
-        <v>-3.015989380000001</v>
+        <v>-3.1072491676</v>
       </c>
       <c r="P52">
-        <v>-14.72512462</v>
+        <v>-15.1706871124</v>
       </c>
       <c r="Q52">
-        <v>8.674875379999996</v>
+        <v>8.229312887599997</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3908723430964665</v>
+        <v>0.397914635812721</v>
       </c>
       <c r="T52">
-        <v>1.235814442302625</v>
+        <v>1.26103514520676</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.05763546177703355</v>
+        <v>0.05650535468336623</v>
       </c>
       <c r="W52">
-        <v>0.2222095581129755</v>
+        <v>0.2224760373656622</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3390321281001973</v>
+        <v>0.3323844393139189</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.308440950604721</v>
+        <v>0.310340950604721</v>
       </c>
       <c r="C53">
-        <v>81.14821855617964</v>
+        <v>78.34971504360337</v>
       </c>
       <c r="D53">
-        <v>84.65481855617968</v>
+        <v>84.1329150436034</v>
       </c>
       <c r="E53">
-        <v>108.2466</v>
+        <v>110.5232</v>
       </c>
       <c r="F53">
-        <v>116.1066</v>
+        <v>118.3832</v>
       </c>
       <c r="G53">
         <v>112.6</v>
@@ -5621,37 +5621,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M53">
-        <v>27.37793628</v>
+        <v>27.91475856000001</v>
       </c>
       <c r="N53">
-        <v>-18.27793628</v>
+        <v>-18.81475856</v>
       </c>
       <c r="O53">
-        <v>-3.1072491676</v>
+        <v>-3.198508955200001</v>
       </c>
       <c r="P53">
-        <v>-15.1706871124</v>
+        <v>-15.6162496048</v>
       </c>
       <c r="Q53">
-        <v>8.229312887599997</v>
+        <v>7.783750395199995</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.397914635812721</v>
+        <v>0.4052503573921526</v>
       </c>
       <c r="T53">
-        <v>1.26103514520676</v>
+        <v>1.287306710731901</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.05650535468336623</v>
+        <v>0.05541871324714764</v>
       </c>
       <c r="W53">
-        <v>0.2224760373656622</v>
+        <v>0.2227322674163226</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3323844393139189</v>
+        <v>0.3259924308655744</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.310340950604721</v>
+        <v>0.3122409506047211</v>
       </c>
       <c r="C54">
-        <v>78.34971504360337</v>
+        <v>75.55760725206034</v>
       </c>
       <c r="D54">
-        <v>84.1329150436034</v>
+        <v>83.61740725206036</v>
       </c>
       <c r="E54">
-        <v>110.5232</v>
+        <v>112.7998</v>
       </c>
       <c r="F54">
-        <v>118.3832</v>
+        <v>120.6598</v>
       </c>
       <c r="G54">
         <v>112.6</v>
@@ -5703,37 +5703,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M54">
-        <v>27.91475856000001</v>
+        <v>28.45158084000001</v>
       </c>
       <c r="N54">
-        <v>-18.81475856</v>
+        <v>-19.35158084</v>
       </c>
       <c r="O54">
-        <v>-3.198508955200001</v>
+        <v>-3.289768742800001</v>
       </c>
       <c r="P54">
-        <v>-15.6162496048</v>
+        <v>-16.0618120972</v>
       </c>
       <c r="Q54">
-        <v>7.783750395199995</v>
+        <v>7.338187902799994</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.4052503573921526</v>
+        <v>0.4128982373366666</v>
       </c>
       <c r="T54">
-        <v>1.287306710731901</v>
+        <v>1.314696215215559</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.05541871324714764</v>
+        <v>0.05437307714814486</v>
       </c>
       <c r="W54">
-        <v>0.2227322674163226</v>
+        <v>0.2229788284084674</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3259924308655744</v>
+        <v>0.319841630283205</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.3122409506047211</v>
+        <v>0.314140950604721</v>
       </c>
       <c r="C55">
-        <v>75.55760725206034</v>
+        <v>72.77177833197743</v>
       </c>
       <c r="D55">
-        <v>83.61740725206036</v>
+        <v>83.10817833197746</v>
       </c>
       <c r="E55">
-        <v>112.7998</v>
+        <v>115.0764</v>
       </c>
       <c r="F55">
-        <v>120.6598</v>
+        <v>122.9364</v>
       </c>
       <c r="G55">
         <v>112.6</v>
@@ -5785,37 +5785,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M55">
-        <v>28.45158084000001</v>
+        <v>28.98840312</v>
       </c>
       <c r="N55">
-        <v>-19.35158084</v>
+        <v>-19.88840312</v>
       </c>
       <c r="O55">
-        <v>-3.289768742800001</v>
+        <v>-3.381028530400001</v>
       </c>
       <c r="P55">
-        <v>-16.0618120972</v>
+        <v>-16.5073745896</v>
       </c>
       <c r="Q55">
-        <v>7.338187902799994</v>
+        <v>6.892625410399997</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.4128982373366666</v>
+        <v>0.4208786338005071</v>
       </c>
       <c r="T55">
-        <v>1.314696215215559</v>
+        <v>1.343276567720245</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.05437307714814486</v>
+        <v>0.0533661683120681</v>
       </c>
       <c r="W55">
-        <v>0.2229788284084674</v>
+        <v>0.2232162575120143</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.319841630283205</v>
+        <v>0.3139186371298124</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.314140950604721</v>
+        <v>0.316040950604721</v>
       </c>
       <c r="C56">
-        <v>72.77177833197743</v>
+        <v>69.99211426300104</v>
       </c>
       <c r="D56">
-        <v>83.10817833197746</v>
+        <v>82.60511426300108</v>
       </c>
       <c r="E56">
-        <v>115.0764</v>
+        <v>117.353</v>
       </c>
       <c r="F56">
-        <v>122.9364</v>
+        <v>125.213</v>
       </c>
       <c r="G56">
         <v>112.6</v>
@@ -5867,37 +5867,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M56">
-        <v>28.98840312</v>
+        <v>29.52522540000001</v>
       </c>
       <c r="N56">
-        <v>-19.88840312</v>
+        <v>-20.42522540000001</v>
       </c>
       <c r="O56">
-        <v>-3.381028530400001</v>
+        <v>-3.472288318000001</v>
       </c>
       <c r="P56">
-        <v>-16.5073745896</v>
+        <v>-16.95293708200001</v>
       </c>
       <c r="Q56">
-        <v>6.892625410399997</v>
+        <v>6.447062917999993</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.4208786338005071</v>
+        <v>0.4292137145516295</v>
       </c>
       <c r="T56">
-        <v>1.343276567720245</v>
+        <v>1.373127158114028</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.0533661683120681</v>
+        <v>0.05239587434275777</v>
       </c>
       <c r="W56">
-        <v>0.2232162575120143</v>
+        <v>0.2234450528299777</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3139186371298124</v>
+        <v>0.308211025545634</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.316040950604721</v>
+        <v>0.3179409506047211</v>
       </c>
       <c r="C57">
-        <v>69.99211426300104</v>
+        <v>67.21850376888446</v>
       </c>
       <c r="D57">
-        <v>82.60511426300108</v>
+        <v>82.10810376888448</v>
       </c>
       <c r="E57">
-        <v>117.353</v>
+        <v>119.6296</v>
       </c>
       <c r="F57">
-        <v>125.213</v>
+        <v>127.4896</v>
       </c>
       <c r="G57">
         <v>112.6</v>
@@ -5949,37 +5949,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M57">
-        <v>29.52522540000001</v>
+        <v>30.06204768000001</v>
       </c>
       <c r="N57">
-        <v>-20.42522540000001</v>
+        <v>-20.96204768</v>
       </c>
       <c r="O57">
-        <v>-3.472288318000001</v>
+        <v>-3.563548105600001</v>
       </c>
       <c r="P57">
-        <v>-16.95293708200001</v>
+        <v>-17.3984995744</v>
       </c>
       <c r="Q57">
-        <v>6.447062917999993</v>
+        <v>6.001500425599996</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.4292137145516295</v>
+        <v>0.4379276626096211</v>
       </c>
       <c r="T57">
-        <v>1.373127158114028</v>
+        <v>1.40433459352571</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.05239587434275777</v>
+        <v>0.05146023372949424</v>
       </c>
       <c r="W57">
-        <v>0.2234450528299777</v>
+        <v>0.2236656768865853</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.308211025545634</v>
+        <v>0.3027072572323191</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.3179409506047211</v>
+        <v>0.319840950604721</v>
       </c>
       <c r="C58">
-        <v>67.21850376888446</v>
+        <v>64.45083823542882</v>
       </c>
       <c r="D58">
-        <v>82.10810376888448</v>
+        <v>81.61703823542885</v>
       </c>
       <c r="E58">
-        <v>119.6296</v>
+        <v>121.9062</v>
       </c>
       <c r="F58">
-        <v>127.4896</v>
+        <v>129.7662</v>
       </c>
       <c r="G58">
         <v>112.6</v>
@@ -6031,37 +6031,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M58">
-        <v>30.06204768000001</v>
+        <v>30.59886996000001</v>
       </c>
       <c r="N58">
-        <v>-20.96204768</v>
+        <v>-21.49886996000001</v>
       </c>
       <c r="O58">
-        <v>-3.563548105600001</v>
+        <v>-3.654807893200001</v>
       </c>
       <c r="P58">
-        <v>-17.3984995744</v>
+        <v>-17.84406206680001</v>
       </c>
       <c r="Q58">
-        <v>6.001500425599996</v>
+        <v>5.555937933199992</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.4379276626096211</v>
+        <v>0.4470469105772867</v>
       </c>
       <c r="T58">
-        <v>1.40433459352571</v>
+        <v>1.436993537561192</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.05146023372949424</v>
+        <v>0.05055742261143294</v>
       </c>
       <c r="W58">
-        <v>0.2236656768865853</v>
+        <v>0.2238785597482241</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3027072572323191</v>
+        <v>0.2973966035966643</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.319840950604721</v>
+        <v>0.321740950604721</v>
       </c>
       <c r="C59">
-        <v>64.45083823542882</v>
+        <v>61.68901163135189</v>
       </c>
       <c r="D59">
-        <v>81.61703823542885</v>
+        <v>81.13181163135192</v>
       </c>
       <c r="E59">
-        <v>121.9062</v>
+        <v>124.1828</v>
       </c>
       <c r="F59">
-        <v>129.7662</v>
+        <v>132.0428</v>
       </c>
       <c r="G59">
         <v>112.6</v>
@@ -6113,37 +6113,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M59">
-        <v>30.59886996000001</v>
+        <v>31.13569224000001</v>
       </c>
       <c r="N59">
-        <v>-21.49886996000001</v>
+        <v>-22.03569224000001</v>
       </c>
       <c r="O59">
-        <v>-3.654807893200001</v>
+        <v>-3.746067680800001</v>
       </c>
       <c r="P59">
-        <v>-17.84406206680001</v>
+        <v>-18.28962455920001</v>
       </c>
       <c r="Q59">
-        <v>5.555937933199992</v>
+        <v>5.110375440799992</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.4470469105772867</v>
+        <v>0.4566004084481745</v>
       </c>
       <c r="T59">
-        <v>1.436993537561192</v>
+        <v>1.471207669407887</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.05055742261143294</v>
+        <v>0.04968574291123581</v>
       </c>
       <c r="W59">
-        <v>0.2238785597482241</v>
+        <v>0.2240841018215306</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2973966035966643</v>
+        <v>0.292269075948446</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.321740950604721</v>
+        <v>0.323640950604721</v>
       </c>
       <c r="C60">
-        <v>61.68901163135192</v>
+        <v>58.9329204319624</v>
       </c>
       <c r="D60">
-        <v>81.13181163135192</v>
+        <v>80.65232043196241</v>
       </c>
       <c r="E60">
-        <v>124.1828</v>
+        <v>126.4594</v>
       </c>
       <c r="F60">
-        <v>132.0428</v>
+        <v>134.3194</v>
       </c>
       <c r="G60">
         <v>112.6</v>
@@ -6195,37 +6195,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M60">
-        <v>31.13569224</v>
+        <v>31.67251452</v>
       </c>
       <c r="N60">
-        <v>-22.03569224</v>
+        <v>-22.57251452</v>
       </c>
       <c r="O60">
-        <v>-3.7460676808</v>
+        <v>-3.8373274684</v>
       </c>
       <c r="P60">
-        <v>-18.2896245592</v>
+        <v>-18.7351870516</v>
       </c>
       <c r="Q60">
-        <v>5.110375440799999</v>
+        <v>4.664812948399998</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.4566004084481744</v>
+        <v>0.4666199306054469</v>
       </c>
       <c r="T60">
-        <v>1.471207669407887</v>
+        <v>1.507090783295884</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.04968574291123583</v>
+        <v>0.04884361167545217</v>
       </c>
       <c r="W60">
-        <v>0.2240841018215306</v>
+        <v>0.2242826763669284</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.292269075948446</v>
+        <v>0.2873153627967775</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.323640950604721</v>
+        <v>0.325540950604721</v>
       </c>
       <c r="C61">
-        <v>58.9329204319624</v>
+        <v>56.18246354552508</v>
       </c>
       <c r="D61">
-        <v>80.65232043196241</v>
+        <v>80.17846354552508</v>
       </c>
       <c r="E61">
-        <v>126.4594</v>
+        <v>128.736</v>
       </c>
       <c r="F61">
-        <v>134.3194</v>
+        <v>136.596</v>
       </c>
       <c r="G61">
         <v>112.6</v>
@@ -6277,37 +6277,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M61">
-        <v>31.67251452</v>
+        <v>32.2093368</v>
       </c>
       <c r="N61">
-        <v>-22.57251452</v>
+        <v>-23.1093368</v>
       </c>
       <c r="O61">
-        <v>-3.8373274684</v>
+        <v>-3.928587256000001</v>
       </c>
       <c r="P61">
-        <v>-18.7351870516</v>
+        <v>-19.180749544</v>
       </c>
       <c r="Q61">
-        <v>4.664812948399998</v>
+        <v>4.219250455999997</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.4666199306054469</v>
+        <v>0.4771404288705832</v>
       </c>
       <c r="T61">
-        <v>1.507090783295884</v>
+        <v>1.544768052878281</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.04884361167545217</v>
+        <v>0.0480295514808613</v>
       </c>
       <c r="W61">
-        <v>0.2242826763669284</v>
+        <v>0.2244746317608129</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2873153627967775</v>
+        <v>0.2825267734168311</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.325540950604721</v>
+        <v>0.327440950604721</v>
       </c>
       <c r="C62">
-        <v>56.18246354552508</v>
+        <v>53.43754224220643</v>
       </c>
       <c r="D62">
-        <v>80.17846354552508</v>
+        <v>79.71014224220644</v>
       </c>
       <c r="E62">
-        <v>128.736</v>
+        <v>131.0126</v>
       </c>
       <c r="F62">
-        <v>136.596</v>
+        <v>138.8726</v>
       </c>
       <c r="G62">
         <v>112.6</v>
@@ -6359,37 +6359,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M62">
-        <v>32.2093368</v>
+        <v>32.74615908000001</v>
       </c>
       <c r="N62">
-        <v>-23.1093368</v>
+        <v>-23.64615908</v>
       </c>
       <c r="O62">
-        <v>-3.928587256000001</v>
+        <v>-4.019847043600001</v>
       </c>
       <c r="P62">
-        <v>-19.180749544</v>
+        <v>-19.6263120364</v>
       </c>
       <c r="Q62">
-        <v>4.219250455999997</v>
+        <v>3.773687963599997</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.4771404288705832</v>
+        <v>0.4882004398672647</v>
       </c>
       <c r="T62">
-        <v>1.544768052878281</v>
+        <v>1.584377490131571</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.0480295514808613</v>
+        <v>0.04724218178445373</v>
       </c>
       <c r="W62">
-        <v>0.2244746317608129</v>
+        <v>0.2246602935352258</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2825267734168311</v>
+        <v>0.2778951869673748</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.327440950604721</v>
+        <v>0.329340950604721</v>
       </c>
       <c r="C63">
-        <v>53.43754224220643</v>
+        <v>50.69806008549614</v>
       </c>
       <c r="D63">
-        <v>79.71014224220644</v>
+        <v>79.24726008549614</v>
       </c>
       <c r="E63">
-        <v>131.0126</v>
+        <v>133.2892</v>
       </c>
       <c r="F63">
-        <v>138.8726</v>
+        <v>141.1492</v>
       </c>
       <c r="G63">
         <v>112.6</v>
@@ -6441,37 +6441,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M63">
-        <v>32.74615908000001</v>
+        <v>33.28298136</v>
       </c>
       <c r="N63">
-        <v>-23.64615908</v>
+        <v>-24.18298136</v>
       </c>
       <c r="O63">
-        <v>-4.019847043600001</v>
+        <v>-4.1111068312</v>
       </c>
       <c r="P63">
-        <v>-19.6263120364</v>
+        <v>-20.0718745288</v>
       </c>
       <c r="Q63">
-        <v>3.773687963599997</v>
+        <v>3.3281254712</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.4882004398672647</v>
+        <v>0.499842556705877</v>
       </c>
       <c r="T63">
-        <v>1.584377490131571</v>
+        <v>1.626071634608717</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04724218178445373</v>
+        <v>0.04648021111051093</v>
       </c>
       <c r="W63">
-        <v>0.2246602935352258</v>
+        <v>0.2248399662201415</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2778951869673748</v>
+        <v>0.2734130065324173</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.329340950604721</v>
+        <v>0.331240950604721</v>
       </c>
       <c r="C64">
-        <v>50.69806008549614</v>
+        <v>47.96392286600397</v>
       </c>
       <c r="D64">
-        <v>79.24726008549614</v>
+        <v>78.78972286600398</v>
       </c>
       <c r="E64">
-        <v>133.2892</v>
+        <v>135.5658</v>
       </c>
       <c r="F64">
-        <v>141.1492</v>
+        <v>143.4258</v>
       </c>
       <c r="G64">
         <v>112.6</v>
@@ -6523,37 +6523,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M64">
-        <v>33.28298136</v>
+        <v>33.81980364</v>
       </c>
       <c r="N64">
-        <v>-24.18298136</v>
+        <v>-24.71980364</v>
       </c>
       <c r="O64">
-        <v>-4.1111068312</v>
+        <v>-4.202366618800001</v>
       </c>
       <c r="P64">
-        <v>-20.0718745288</v>
+        <v>-20.5174370212</v>
       </c>
       <c r="Q64">
-        <v>3.3281254712</v>
+        <v>2.882562978799996</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.499842556705877</v>
+        <v>0.5121139771573872</v>
       </c>
       <c r="T64">
-        <v>1.626071634608717</v>
+        <v>1.670019516625169</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04648021111051093</v>
+        <v>0.04574242998177266</v>
       </c>
       <c r="W64">
-        <v>0.2248399662201415</v>
+        <v>0.225013935010298</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2734130065324173</v>
+        <v>0.2690731175398392</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.331240950604721</v>
+        <v>0.333140950604721</v>
       </c>
       <c r="C65">
-        <v>47.96392286600397</v>
+        <v>45.23503853753721</v>
       </c>
       <c r="D65">
-        <v>78.78972286600398</v>
+        <v>78.33743853753721</v>
       </c>
       <c r="E65">
-        <v>135.5658</v>
+        <v>137.8424</v>
       </c>
       <c r="F65">
-        <v>143.4258</v>
+        <v>145.7024</v>
       </c>
       <c r="G65">
         <v>112.6</v>
@@ -6605,37 +6605,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M65">
-        <v>33.81980364</v>
+        <v>34.35662592000001</v>
       </c>
       <c r="N65">
-        <v>-24.71980364</v>
+        <v>-25.25662592</v>
       </c>
       <c r="O65">
-        <v>-4.202366618800001</v>
+        <v>-4.293626406400001</v>
       </c>
       <c r="P65">
-        <v>-20.5174370212</v>
+        <v>-20.9629995136</v>
       </c>
       <c r="Q65">
-        <v>2.882562978799996</v>
+        <v>2.437000486399995</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.5121139771573872</v>
+        <v>0.5250671431895367</v>
       </c>
       <c r="T65">
-        <v>1.670019516625169</v>
+        <v>1.716408947642535</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04574242998177266</v>
+        <v>0.04502770451330746</v>
       </c>
       <c r="W65">
-        <v>0.225013935010298</v>
+        <v>0.2251824672757621</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2690731175398392</v>
+        <v>0.2648688500782792</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.333140950604721</v>
+        <v>0.3350409506047209</v>
       </c>
       <c r="C66">
-        <v>45.23503853753721</v>
+        <v>42.5113171553667</v>
       </c>
       <c r="D66">
-        <v>78.33743853753721</v>
+        <v>77.89031715536672</v>
       </c>
       <c r="E66">
-        <v>137.8424</v>
+        <v>140.119</v>
       </c>
       <c r="F66">
-        <v>145.7024</v>
+        <v>147.979</v>
       </c>
       <c r="G66">
         <v>112.6</v>
@@ -6687,37 +6687,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M66">
-        <v>34.35662592000001</v>
+        <v>34.8934482</v>
       </c>
       <c r="N66">
-        <v>-25.25662592</v>
+        <v>-25.7934482</v>
       </c>
       <c r="O66">
-        <v>-4.293626406400001</v>
+        <v>-4.384886194000001</v>
       </c>
       <c r="P66">
-        <v>-20.9629995136</v>
+        <v>-21.408562006</v>
       </c>
       <c r="Q66">
-        <v>2.437000486399995</v>
+        <v>1.991437993999998</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.5250671431895367</v>
+        <v>0.5387604901378092</v>
       </c>
       <c r="T66">
-        <v>1.716408947642535</v>
+        <v>1.765449203289464</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04502770451330746</v>
+        <v>0.04433497059771813</v>
       </c>
       <c r="W66">
-        <v>0.2251824672757621</v>
+        <v>0.2253458139330581</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2648688500782792</v>
+        <v>0.2607939446924595</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.3350409506047209</v>
+        <v>0.336940950604721</v>
       </c>
       <c r="C67">
-        <v>42.5113171553667</v>
+        <v>39.79267081659546</v>
       </c>
       <c r="D67">
-        <v>77.89031715536672</v>
+        <v>77.44827081659548</v>
       </c>
       <c r="E67">
-        <v>140.119</v>
+        <v>142.3956</v>
       </c>
       <c r="F67">
-        <v>147.979</v>
+        <v>150.2556</v>
       </c>
       <c r="G67">
         <v>112.6</v>
@@ -6769,37 +6769,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M67">
-        <v>34.8934482</v>
+        <v>35.43027048</v>
       </c>
       <c r="N67">
-        <v>-25.7934482</v>
+        <v>-26.33027048</v>
       </c>
       <c r="O67">
-        <v>-4.384886194000001</v>
+        <v>-4.476145981600001</v>
       </c>
       <c r="P67">
-        <v>-21.408562006</v>
+        <v>-21.8541244984</v>
       </c>
       <c r="Q67">
-        <v>1.991437993999998</v>
+        <v>1.545875501599998</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.5387604901378092</v>
+        <v>0.553259328083039</v>
       </c>
       <c r="T67">
-        <v>1.765449203289464</v>
+        <v>1.817374179856802</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04433497059771813</v>
+        <v>0.04366322861896482</v>
       </c>
       <c r="W67">
-        <v>0.2253458139330581</v>
+        <v>0.2255042106916481</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2607939446924595</v>
+        <v>0.2568425212880283</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.336940950604721</v>
+        <v>0.338840950604721</v>
       </c>
       <c r="C68">
-        <v>39.79267081659546</v>
+        <v>37.07901360254627</v>
       </c>
       <c r="D68">
-        <v>77.44827081659548</v>
+        <v>77.01121360254631</v>
       </c>
       <c r="E68">
-        <v>142.3956</v>
+        <v>144.6722</v>
       </c>
       <c r="F68">
-        <v>150.2556</v>
+        <v>152.5322</v>
       </c>
       <c r="G68">
         <v>112.6</v>
@@ -6851,37 +6851,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M68">
-        <v>35.43027048</v>
+        <v>35.96709276000001</v>
       </c>
       <c r="N68">
-        <v>-26.33027048</v>
+        <v>-26.86709276000001</v>
       </c>
       <c r="O68">
-        <v>-4.476145981600001</v>
+        <v>-4.567405769200001</v>
       </c>
       <c r="P68">
-        <v>-21.8541244984</v>
+        <v>-22.29968699080001</v>
       </c>
       <c r="Q68">
-        <v>1.545875501599998</v>
+        <v>1.100313009199994</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.553259328083039</v>
+        <v>0.5686368834794947</v>
       </c>
       <c r="T68">
-        <v>1.817374179856802</v>
+        <v>1.872446124700947</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04366322861896482</v>
+        <v>0.04301153863957728</v>
       </c>
       <c r="W68">
-        <v>0.2255042106916481</v>
+        <v>0.2256578791887877</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2568425212880283</v>
+        <v>0.2530090508210427</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.338840950604721</v>
+        <v>0.340740950604721</v>
       </c>
       <c r="C69">
-        <v>37.07901360254627</v>
+        <v>34.37026152308871</v>
       </c>
       <c r="D69">
-        <v>77.01121360254631</v>
+        <v>76.57906152308874</v>
       </c>
       <c r="E69">
-        <v>144.6722</v>
+        <v>146.9488</v>
       </c>
       <c r="F69">
-        <v>152.5322</v>
+        <v>154.8088</v>
       </c>
       <c r="G69">
         <v>112.6</v>
@@ -6933,37 +6933,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M69">
-        <v>35.96709276000001</v>
+        <v>36.50391504</v>
       </c>
       <c r="N69">
-        <v>-26.86709276000001</v>
+        <v>-27.40391504</v>
       </c>
       <c r="O69">
-        <v>-4.567405769200001</v>
+        <v>-4.658665556800001</v>
       </c>
       <c r="P69">
-        <v>-22.29968699080001</v>
+        <v>-22.7452494832</v>
       </c>
       <c r="Q69">
-        <v>1.100313009199994</v>
+        <v>0.6547505168000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.5686368834794947</v>
+        <v>0.5849755360882291</v>
       </c>
       <c r="T69">
-        <v>1.872446124700947</v>
+        <v>1.930960066097852</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04301153863957728</v>
+        <v>0.04237901601252467</v>
       </c>
       <c r="W69">
-        <v>0.2256578791887877</v>
+        <v>0.2258070280242467</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2530090508210427</v>
+        <v>0.2492883294854392</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.340740950604721</v>
+        <v>0.342640950604721</v>
       </c>
       <c r="C70">
-        <v>34.37026152308871</v>
+        <v>31.66633246283067</v>
       </c>
       <c r="D70">
-        <v>76.57906152308874</v>
+        <v>76.15173246283069</v>
       </c>
       <c r="E70">
-        <v>146.9488</v>
+        <v>149.2254</v>
       </c>
       <c r="F70">
-        <v>154.8088</v>
+        <v>157.0854</v>
       </c>
       <c r="G70">
         <v>112.6</v>
@@ -7015,37 +7015,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M70">
-        <v>36.50391504</v>
+        <v>37.04073732000001</v>
       </c>
       <c r="N70">
-        <v>-27.40391504</v>
+        <v>-27.94073732</v>
       </c>
       <c r="O70">
-        <v>-4.658665556800001</v>
+        <v>-4.749925344400001</v>
       </c>
       <c r="P70">
-        <v>-22.7452494832</v>
+        <v>-23.1908119756</v>
       </c>
       <c r="Q70">
-        <v>0.6547505168000001</v>
+        <v>0.209188024399996</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.5849755360882291</v>
+        <v>0.6023682953168815</v>
       </c>
       <c r="T70">
-        <v>1.930960066097852</v>
+        <v>1.993249100488105</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04237901601252467</v>
+        <v>0.04176482737466199</v>
       </c>
       <c r="W70">
-        <v>0.2258070280242467</v>
+        <v>0.2259518537050547</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2492883294854392</v>
+        <v>0.2456754551450705</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.342640950604721</v>
+        <v>0.344540950604721</v>
       </c>
       <c r="C71">
-        <v>31.66633246283067</v>
+        <v>28.96714612910108</v>
       </c>
       <c r="D71">
-        <v>76.15173246283069</v>
+        <v>75.72914612910112</v>
       </c>
       <c r="E71">
-        <v>149.2254</v>
+        <v>151.502</v>
       </c>
       <c r="F71">
-        <v>157.0854</v>
+        <v>159.362</v>
       </c>
       <c r="G71">
         <v>112.6</v>
@@ -7097,37 +7097,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M71">
-        <v>37.04073732000001</v>
+        <v>37.57755960000001</v>
       </c>
       <c r="N71">
-        <v>-27.94073732</v>
+        <v>-28.47755960000001</v>
       </c>
       <c r="O71">
-        <v>-4.749925344400001</v>
+        <v>-4.841185132000001</v>
       </c>
       <c r="P71">
-        <v>-23.1908119756</v>
+        <v>-23.63637446800001</v>
       </c>
       <c r="Q71">
-        <v>0.209188024399996</v>
+        <v>-0.2363744680000082</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.6023682953168815</v>
+        <v>0.6209205718274443</v>
       </c>
       <c r="T71">
-        <v>1.993249100488105</v>
+        <v>2.059690737171042</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04176482737466199</v>
+        <v>0.04116818698359539</v>
       </c>
       <c r="W71">
-        <v>0.2259518537050547</v>
+        <v>0.2260925415092682</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2456754551450705</v>
+        <v>0.2421658057858552</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.344540950604721</v>
+        <v>0.346440950604721</v>
       </c>
       <c r="C72">
-        <v>28.96714612910108</v>
+        <v>26.27262400165534</v>
       </c>
       <c r="D72">
-        <v>75.72914612910112</v>
+        <v>75.31122400165538</v>
       </c>
       <c r="E72">
-        <v>151.502</v>
+        <v>153.7786</v>
       </c>
       <c r="F72">
-        <v>159.362</v>
+        <v>161.6386</v>
       </c>
       <c r="G72">
         <v>112.6</v>
@@ -7179,37 +7179,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M72">
-        <v>37.57755960000001</v>
+        <v>38.11438188000001</v>
       </c>
       <c r="N72">
-        <v>-28.47755960000001</v>
+        <v>-29.01438188000001</v>
       </c>
       <c r="O72">
-        <v>-4.841185132000001</v>
+        <v>-4.932444919600002</v>
       </c>
       <c r="P72">
-        <v>-23.63637446800001</v>
+        <v>-24.08193696040001</v>
       </c>
       <c r="Q72">
-        <v>-0.2363744680000082</v>
+        <v>-0.6819369604000087</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.6209205718274443</v>
+        <v>0.6407523156835632</v>
       </c>
       <c r="T72">
-        <v>2.059690737171042</v>
+        <v>2.130714555694182</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04116818698359539</v>
+        <v>0.04058835336410813</v>
       </c>
       <c r="W72">
-        <v>0.2260925415092682</v>
+        <v>0.2262292662767433</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2421658057858552</v>
+        <v>0.2387550197888714</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.346440950604721</v>
+        <v>0.348340950604721</v>
       </c>
       <c r="C73">
-        <v>26.27262400165537</v>
+        <v>23.58268928403663</v>
       </c>
       <c r="D73">
-        <v>75.31122400165538</v>
+        <v>74.89788928403664</v>
       </c>
       <c r="E73">
-        <v>153.7786</v>
+        <v>156.0552</v>
       </c>
       <c r="F73">
-        <v>161.6386</v>
+        <v>163.9152</v>
       </c>
       <c r="G73">
         <v>112.6</v>
@@ -7261,37 +7261,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M73">
-        <v>38.11438188</v>
+        <v>38.65120416</v>
       </c>
       <c r="N73">
-        <v>-29.01438188</v>
+        <v>-29.55120416</v>
       </c>
       <c r="O73">
-        <v>-4.932444919600001</v>
+        <v>-5.0237047072</v>
       </c>
       <c r="P73">
-        <v>-24.0819369604</v>
+        <v>-24.5274994528</v>
       </c>
       <c r="Q73">
-        <v>-0.6819369604000016</v>
+        <v>-1.127499452799999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.6407523156835629</v>
+        <v>0.6620006126722615</v>
       </c>
       <c r="T73">
-        <v>2.130714555694181</v>
+        <v>2.20681150411183</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04058835336410813</v>
+        <v>0.04002462623405108</v>
       </c>
       <c r="W73">
-        <v>0.2262292662767433</v>
+        <v>0.2263621931340108</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2387550197888714</v>
+        <v>0.2354389778473593</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.348340950604721</v>
+        <v>0.350240950604721</v>
       </c>
       <c r="C74">
-        <v>23.58268928403663</v>
+        <v>20.89726685653034</v>
       </c>
       <c r="D74">
-        <v>74.89788928403664</v>
+        <v>74.48906685653034</v>
       </c>
       <c r="E74">
-        <v>156.0552</v>
+        <v>158.3318</v>
       </c>
       <c r="F74">
-        <v>163.9152</v>
+        <v>166.1918</v>
       </c>
       <c r="G74">
         <v>112.6</v>
@@ -7343,37 +7343,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M74">
-        <v>38.65120416</v>
+        <v>39.18802644</v>
       </c>
       <c r="N74">
-        <v>-29.55120416</v>
+        <v>-30.08802644</v>
       </c>
       <c r="O74">
-        <v>-5.0237047072</v>
+        <v>-5.114964494800001</v>
       </c>
       <c r="P74">
-        <v>-24.5274994528</v>
+        <v>-24.9730619452</v>
       </c>
       <c r="Q74">
-        <v>-1.127499452799999</v>
+        <v>-1.573061945200003</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.6620006126722615</v>
+        <v>0.684822857586049</v>
       </c>
       <c r="T74">
-        <v>2.20681150411183</v>
+        <v>2.28854526352338</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04002462623405108</v>
+        <v>0.0394763436828997</v>
       </c>
       <c r="W74">
-        <v>0.2263621931340108</v>
+        <v>0.2264914781595723</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2354389778473593</v>
+        <v>0.2322137863699982</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.350240950604721</v>
+        <v>0.352140950604721</v>
       </c>
       <c r="C75">
-        <v>20.89726685653034</v>
+        <v>18.21628323065096</v>
       </c>
       <c r="D75">
-        <v>74.48906685653034</v>
+        <v>74.08468323065097</v>
       </c>
       <c r="E75">
-        <v>158.3318</v>
+        <v>160.6084</v>
       </c>
       <c r="F75">
-        <v>166.1918</v>
+        <v>168.4684</v>
       </c>
       <c r="G75">
         <v>112.6</v>
@@ -7425,37 +7425,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M75">
-        <v>39.18802644</v>
+        <v>39.72484872</v>
       </c>
       <c r="N75">
-        <v>-30.08802644</v>
+        <v>-30.62484872</v>
       </c>
       <c r="O75">
-        <v>-5.114964494800001</v>
+        <v>-5.206224282400001</v>
       </c>
       <c r="P75">
-        <v>-24.9730619452</v>
+        <v>-25.4186244376</v>
       </c>
       <c r="Q75">
-        <v>-1.573061945200003</v>
+        <v>-2.018624437600003</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.684822857586049</v>
+        <v>0.7094006598008971</v>
       </c>
       <c r="T75">
-        <v>2.28854526352338</v>
+        <v>2.376566235197356</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.0394763436828997</v>
+        <v>0.03894287957907672</v>
       </c>
       <c r="W75">
-        <v>0.2264914781595723</v>
+        <v>0.2266172689952537</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2322137863699982</v>
+        <v>0.229075762229863</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.352140950604721</v>
+        <v>0.354040950604721</v>
       </c>
       <c r="C76">
-        <v>18.21628323065096</v>
+        <v>15.53966650510336</v>
       </c>
       <c r="D76">
-        <v>74.08468323065097</v>
+        <v>73.68466650510337</v>
       </c>
       <c r="E76">
-        <v>160.6084</v>
+        <v>162.885</v>
       </c>
       <c r="F76">
-        <v>168.4684</v>
+        <v>170.745</v>
       </c>
       <c r="G76">
         <v>112.6</v>
@@ -7507,37 +7507,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M76">
-        <v>39.72484872</v>
+        <v>40.261671</v>
       </c>
       <c r="N76">
-        <v>-30.62484872</v>
+        <v>-31.161671</v>
       </c>
       <c r="O76">
-        <v>-5.206224282400001</v>
+        <v>-5.29748407</v>
       </c>
       <c r="P76">
-        <v>-25.4186244376</v>
+        <v>-25.86418693</v>
       </c>
       <c r="Q76">
-        <v>-2.018624437600003</v>
+        <v>-2.46418693</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.7094006598008971</v>
+        <v>0.7359446861929331</v>
       </c>
       <c r="T76">
-        <v>2.376566235197356</v>
+        <v>2.47162888460525</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03894287957907672</v>
+        <v>0.03842364118468904</v>
       </c>
       <c r="W76">
-        <v>0.2266172689952537</v>
+        <v>0.2267397054086503</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.229075762229863</v>
+        <v>0.2260214187334649</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.354040950604721</v>
+        <v>0.355940950604721</v>
       </c>
       <c r="C77">
-        <v>15.53966650510336</v>
+        <v>12.86734632316299</v>
       </c>
       <c r="D77">
-        <v>73.68466650510337</v>
+        <v>73.28894632316303</v>
       </c>
       <c r="E77">
-        <v>162.885</v>
+        <v>165.1616</v>
       </c>
       <c r="F77">
-        <v>170.745</v>
+        <v>173.0216</v>
       </c>
       <c r="G77">
         <v>112.6</v>
@@ -7589,37 +7589,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M77">
-        <v>40.261671</v>
+        <v>40.79849328000001</v>
       </c>
       <c r="N77">
-        <v>-31.161671</v>
+        <v>-31.69849328000001</v>
       </c>
       <c r="O77">
-        <v>-5.29748407</v>
+        <v>-5.388743857600002</v>
       </c>
       <c r="P77">
-        <v>-25.86418693</v>
+        <v>-26.30974942240001</v>
       </c>
       <c r="Q77">
-        <v>-2.46418693</v>
+        <v>-2.909749422400008</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.7359446861929331</v>
+        <v>0.7647007147843052</v>
       </c>
       <c r="T77">
-        <v>2.47162888460525</v>
+        <v>2.574613421463802</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03842364118468904</v>
+        <v>0.0379180669585747</v>
       </c>
       <c r="W77">
-        <v>0.2267397054086503</v>
+        <v>0.2268589198111681</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2260214187334649</v>
+        <v>0.2230474526974983</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.355940950604721</v>
+        <v>0.357840950604721</v>
       </c>
       <c r="C78">
-        <v>12.86734632316299</v>
+        <v>10.1992538314224</v>
       </c>
       <c r="D78">
-        <v>73.28894632316303</v>
+        <v>72.89745383142242</v>
       </c>
       <c r="E78">
-        <v>165.1616</v>
+        <v>167.4382</v>
       </c>
       <c r="F78">
-        <v>173.0216</v>
+        <v>175.2982</v>
       </c>
       <c r="G78">
         <v>112.6</v>
@@ -7671,37 +7671,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M78">
-        <v>40.79849328000001</v>
+        <v>41.33531556000001</v>
       </c>
       <c r="N78">
-        <v>-31.69849328000001</v>
+        <v>-32.23531556000001</v>
       </c>
       <c r="O78">
-        <v>-5.388743857600002</v>
+        <v>-5.480003645200002</v>
       </c>
       <c r="P78">
-        <v>-26.30974942240001</v>
+        <v>-26.75531191480001</v>
       </c>
       <c r="Q78">
-        <v>-2.909749422400008</v>
+        <v>-3.355311914800012</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.7647007147843052</v>
+        <v>0.7959572676010142</v>
       </c>
       <c r="T78">
-        <v>2.574613421463802</v>
+        <v>2.686553135440489</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.0379180669585747</v>
+        <v>0.03742562453054126</v>
       </c>
       <c r="W78">
-        <v>0.2268589198111681</v>
+        <v>0.2269750377356984</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2230474526974983</v>
+        <v>0.2201507325325956</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.357840950604721</v>
+        <v>0.359740950604721</v>
       </c>
       <c r="C79">
-        <v>10.1992538314224</v>
+        <v>7.535321639852469</v>
       </c>
       <c r="D79">
-        <v>72.89745383142242</v>
+        <v>72.51012163985251</v>
       </c>
       <c r="E79">
-        <v>167.4382</v>
+        <v>169.7148</v>
       </c>
       <c r="F79">
-        <v>175.2982</v>
+        <v>177.5748</v>
       </c>
       <c r="G79">
         <v>112.6</v>
@@ -7753,37 +7753,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M79">
-        <v>41.33531556000001</v>
+        <v>41.87213784000001</v>
       </c>
       <c r="N79">
-        <v>-32.23531556000001</v>
+        <v>-32.77213784000001</v>
       </c>
       <c r="O79">
-        <v>-5.480003645200002</v>
+        <v>-5.571263432800001</v>
       </c>
       <c r="P79">
-        <v>-26.75531191480001</v>
+        <v>-27.2008744072</v>
       </c>
       <c r="Q79">
-        <v>-3.355311914800012</v>
+        <v>-3.800874407200006</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.7959572676010142</v>
+        <v>0.8300553252192421</v>
       </c>
       <c r="T79">
-        <v>2.686553135440489</v>
+        <v>2.808669187051421</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03742562453054126</v>
+        <v>0.03694580883143176</v>
       </c>
       <c r="W79">
-        <v>0.2269750377356984</v>
+        <v>0.2270881782775484</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2201507325325956</v>
+        <v>0.2173282872437162</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.359740950604721</v>
+        <v>0.361640950604721</v>
       </c>
       <c r="C80">
-        <v>7.535321639852469</v>
+        <v>4.875483783130704</v>
       </c>
       <c r="D80">
-        <v>72.51012163985251</v>
+        <v>72.12688378313076</v>
       </c>
       <c r="E80">
-        <v>169.7148</v>
+        <v>171.9914</v>
       </c>
       <c r="F80">
-        <v>177.5748</v>
+        <v>179.8514</v>
       </c>
       <c r="G80">
         <v>112.6</v>
@@ -7835,37 +7835,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M80">
-        <v>41.87213784000001</v>
+        <v>42.40896012000001</v>
       </c>
       <c r="N80">
-        <v>-32.77213784000001</v>
+        <v>-33.30896012000001</v>
       </c>
       <c r="O80">
-        <v>-5.571263432800001</v>
+        <v>-5.662523220400002</v>
       </c>
       <c r="P80">
-        <v>-27.2008744072</v>
+        <v>-27.64643689960001</v>
       </c>
       <c r="Q80">
-        <v>-3.800874407200006</v>
+        <v>-4.24643689960001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.8300553252192421</v>
+        <v>0.8674008168963488</v>
       </c>
       <c r="T80">
-        <v>2.808669187051421</v>
+        <v>2.942415338815774</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03694580883143176</v>
+        <v>0.0364781403652111</v>
       </c>
       <c r="W80">
-        <v>0.2270881782775484</v>
+        <v>0.2271984545018832</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2173282872437162</v>
+        <v>0.2145772962659477</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.361640950604721</v>
+        <v>0.363540950604721</v>
       </c>
       <c r="C81">
-        <v>4.875483783130704</v>
+        <v>2.219675683188967</v>
       </c>
       <c r="D81">
-        <v>72.12688378313076</v>
+        <v>71.74767568318902</v>
       </c>
       <c r="E81">
-        <v>171.9914</v>
+        <v>174.268</v>
       </c>
       <c r="F81">
-        <v>179.8514</v>
+        <v>182.128</v>
       </c>
       <c r="G81">
         <v>112.6</v>
@@ -7917,37 +7917,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M81">
-        <v>42.40896012000001</v>
+        <v>42.94578240000001</v>
       </c>
       <c r="N81">
-        <v>-33.30896012000001</v>
+        <v>-33.84578240000001</v>
       </c>
       <c r="O81">
-        <v>-5.662523220400002</v>
+        <v>-5.753783008000003</v>
       </c>
       <c r="P81">
-        <v>-27.64643689960001</v>
+        <v>-28.09199939200001</v>
       </c>
       <c r="Q81">
-        <v>-4.24643689960001</v>
+        <v>-4.69199939200001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.8674008168963488</v>
+        <v>0.9084808577411664</v>
       </c>
       <c r="T81">
-        <v>2.942415338815774</v>
+        <v>3.089536105756563</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.0364781403652111</v>
+        <v>0.03602216361064597</v>
       </c>
       <c r="W81">
-        <v>0.2271984545018832</v>
+        <v>0.2273059738206097</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2145772962659477</v>
+        <v>0.2118950800626233</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.363540950604721</v>
+        <v>0.365440950604721</v>
       </c>
       <c r="C82">
-        <v>2.219675683188967</v>
+        <v>-0.4321658870632916</v>
       </c>
       <c r="D82">
-        <v>71.74767568318902</v>
+        <v>71.37243411293676</v>
       </c>
       <c r="E82">
-        <v>174.268</v>
+        <v>176.5446</v>
       </c>
       <c r="F82">
-        <v>182.128</v>
+        <v>184.4046</v>
       </c>
       <c r="G82">
         <v>112.6</v>
@@ -7999,37 +7999,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M82">
-        <v>42.94578240000001</v>
+        <v>43.48260468000002</v>
       </c>
       <c r="N82">
-        <v>-33.84578240000001</v>
+        <v>-34.38260468000001</v>
       </c>
       <c r="O82">
-        <v>-5.753783008000003</v>
+        <v>-5.845042795600003</v>
       </c>
       <c r="P82">
-        <v>-28.09199939200001</v>
+        <v>-28.53756188440001</v>
       </c>
       <c r="Q82">
-        <v>-4.69199939200001</v>
+        <v>-5.137561884400014</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.9084808577411664</v>
+        <v>0.9538851134117541</v>
       </c>
       <c r="T82">
-        <v>3.089536105756563</v>
+        <v>3.252143269217435</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03602216361064597</v>
+        <v>0.03557744554137873</v>
       </c>
       <c r="W82">
-        <v>0.2273059738206097</v>
+        <v>0.2274108383413429</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2118950800626233</v>
+        <v>0.2092790914198749</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.365440950604721</v>
+        <v>0.367340950604721</v>
       </c>
       <c r="C83">
-        <v>-0.4321658870632916</v>
+        <v>-3.080102838883363</v>
       </c>
       <c r="D83">
-        <v>71.37243411293676</v>
+        <v>71.00109716111669</v>
       </c>
       <c r="E83">
-        <v>176.5446</v>
+        <v>178.8212</v>
       </c>
       <c r="F83">
-        <v>184.4046</v>
+        <v>186.6812</v>
       </c>
       <c r="G83">
         <v>112.6</v>
@@ -8081,37 +8081,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M83">
-        <v>43.48260468000002</v>
+        <v>44.01942696000001</v>
       </c>
       <c r="N83">
-        <v>-34.38260468000001</v>
+        <v>-34.91942696000001</v>
       </c>
       <c r="O83">
-        <v>-5.845042795600003</v>
+        <v>-5.936302583200002</v>
       </c>
       <c r="P83">
-        <v>-28.53756188440001</v>
+        <v>-28.98312437680001</v>
       </c>
       <c r="Q83">
-        <v>-5.137561884400014</v>
+        <v>-5.583124376800008</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.9538851134117541</v>
+        <v>1.004334286379074</v>
       </c>
       <c r="T83">
-        <v>3.252143269217435</v>
+        <v>3.432817895285071</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03557744554137873</v>
+        <v>0.03514357425428875</v>
       </c>
       <c r="W83">
-        <v>0.2274108383413429</v>
+        <v>0.2275131451908387</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2092790914198749</v>
+        <v>0.2067269073781691</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.367340950604721</v>
+        <v>0.369240950604721</v>
       </c>
       <c r="C84">
-        <v>-3.080102838883363</v>
+        <v>-5.724195801748294</v>
       </c>
       <c r="D84">
-        <v>71.00109716111669</v>
+        <v>70.63360419825176</v>
       </c>
       <c r="E84">
-        <v>178.8212</v>
+        <v>181.0978</v>
       </c>
       <c r="F84">
-        <v>186.6812</v>
+        <v>188.9578</v>
       </c>
       <c r="G84">
         <v>112.6</v>
@@ -8163,37 +8163,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M84">
-        <v>44.01942696000001</v>
+        <v>44.55624924000001</v>
       </c>
       <c r="N84">
-        <v>-34.91942696000001</v>
+        <v>-35.45624924000001</v>
       </c>
       <c r="O84">
-        <v>-5.936302583200002</v>
+        <v>-6.027562370800003</v>
       </c>
       <c r="P84">
-        <v>-28.98312437680001</v>
+        <v>-29.42868686920001</v>
       </c>
       <c r="Q84">
-        <v>-5.583124376800008</v>
+        <v>-6.028686869200012</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>1.004334286379074</v>
+        <v>1.060718656166078</v>
       </c>
       <c r="T84">
-        <v>3.432817895285071</v>
+        <v>3.634748359713604</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03514357425428875</v>
+        <v>0.03472015769700815</v>
       </c>
       <c r="W84">
-        <v>0.2275131451908387</v>
+        <v>0.2276129868150455</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2067269073781691</v>
+        <v>0.2042362217471068</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.369240950604721</v>
+        <v>0.3711409506047211</v>
       </c>
       <c r="C85">
-        <v>-5.724195801748294</v>
+        <v>-8.364504156355707</v>
       </c>
       <c r="D85">
-        <v>70.63360419825176</v>
+        <v>70.26989584364435</v>
       </c>
       <c r="E85">
-        <v>181.0978</v>
+        <v>183.3744</v>
       </c>
       <c r="F85">
-        <v>188.9578</v>
+        <v>191.2344000000001</v>
       </c>
       <c r="G85">
         <v>112.6</v>
@@ -8245,37 +8245,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M85">
-        <v>44.55624924000001</v>
+        <v>45.09307152000002</v>
       </c>
       <c r="N85">
-        <v>-35.45624924000001</v>
+        <v>-35.99307152000002</v>
       </c>
       <c r="O85">
-        <v>-6.027562370800003</v>
+        <v>-6.118822158400003</v>
       </c>
       <c r="P85">
-        <v>-29.42868686920001</v>
+        <v>-29.87424936160001</v>
       </c>
       <c r="Q85">
-        <v>-6.028686869200012</v>
+        <v>-6.474249361600013</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>1.060718656166078</v>
+        <v>1.124151072176458</v>
       </c>
       <c r="T85">
-        <v>3.634748359713604</v>
+        <v>3.861920132195706</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03472015769700815</v>
+        <v>0.03430682248632948</v>
       </c>
       <c r="W85">
-        <v>0.2276129868150455</v>
+        <v>0.2277104512577235</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2042362217471068</v>
+        <v>0.2018048381548794</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.371140950604721</v>
+        <v>0.373040950604721</v>
       </c>
       <c r="C86">
-        <v>-8.364504156355679</v>
+        <v>-11.0010860666103</v>
       </c>
       <c r="D86">
-        <v>70.26989584364435</v>
+        <v>69.90991393338972</v>
       </c>
       <c r="E86">
-        <v>183.3744</v>
+        <v>185.651</v>
       </c>
       <c r="F86">
-        <v>191.2344</v>
+        <v>193.511</v>
       </c>
       <c r="G86">
         <v>112.6</v>
@@ -8327,37 +8327,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M86">
-        <v>45.09307152000001</v>
+        <v>45.6298938</v>
       </c>
       <c r="N86">
-        <v>-35.99307152000001</v>
+        <v>-36.5298938</v>
       </c>
       <c r="O86">
-        <v>-6.118822158400002</v>
+        <v>-6.210081946000001</v>
       </c>
       <c r="P86">
-        <v>-29.87424936160001</v>
+        <v>-30.319811854</v>
       </c>
       <c r="Q86">
-        <v>-6.474249361600009</v>
+        <v>-6.919811854000002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>1.124151072176458</v>
+        <v>1.196041143654888</v>
       </c>
       <c r="T86">
-        <v>3.861920132195703</v>
+        <v>4.119381474342083</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03430682248632949</v>
+        <v>0.03390321281001973</v>
       </c>
       <c r="W86">
-        <v>0.2277104512577235</v>
+        <v>0.2278056224193974</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2018048381548794</v>
+        <v>0.1994306635883514</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.373040950604721</v>
+        <v>0.374940950604721</v>
       </c>
       <c r="C87">
-        <v>-11.0010860666103</v>
+        <v>-13.63399851063252</v>
       </c>
       <c r="D87">
-        <v>69.90991393338972</v>
+        <v>69.55360148936751</v>
       </c>
       <c r="E87">
-        <v>185.651</v>
+        <v>187.9276</v>
       </c>
       <c r="F87">
-        <v>193.511</v>
+        <v>195.7876</v>
       </c>
       <c r="G87">
         <v>112.6</v>
@@ -8409,37 +8409,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M87">
-        <v>45.6298938</v>
+        <v>46.16671608000001</v>
       </c>
       <c r="N87">
-        <v>-36.5298938</v>
+        <v>-37.06671608000001</v>
       </c>
       <c r="O87">
-        <v>-6.210081946000001</v>
+        <v>-6.301341733600002</v>
       </c>
       <c r="P87">
-        <v>-30.319811854</v>
+        <v>-30.76537434640001</v>
       </c>
       <c r="Q87">
-        <v>-6.919811854000002</v>
+        <v>-7.365374346400007</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>1.196041143654888</v>
+        <v>1.278201225344523</v>
       </c>
       <c r="T87">
-        <v>4.119381474342083</v>
+        <v>4.41362300822366</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03390321281001973</v>
+        <v>0.03350898940525206</v>
       </c>
       <c r="W87">
-        <v>0.2278056224193974</v>
+        <v>0.2278985802982416</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1994306635883514</v>
+        <v>0.1971117023838357</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.374940950604721</v>
+        <v>0.376840950604721</v>
       </c>
       <c r="C88">
-        <v>-13.63399851063252</v>
+        <v>-16.26329731082296</v>
       </c>
       <c r="D88">
-        <v>69.55360148936751</v>
+        <v>69.20090268917708</v>
       </c>
       <c r="E88">
-        <v>187.9276</v>
+        <v>190.2042</v>
       </c>
       <c r="F88">
-        <v>195.7876</v>
+        <v>198.0642</v>
       </c>
       <c r="G88">
         <v>112.6</v>
@@ -8491,37 +8491,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M88">
-        <v>46.16671608000001</v>
+        <v>46.70353836000001</v>
       </c>
       <c r="N88">
-        <v>-37.06671608000001</v>
+        <v>-37.60353836000001</v>
       </c>
       <c r="O88">
-        <v>-6.301341733600002</v>
+        <v>-6.392601521200002</v>
       </c>
       <c r="P88">
-        <v>-30.76537434640001</v>
+        <v>-31.21093683880001</v>
       </c>
       <c r="Q88">
-        <v>-7.365374346400007</v>
+        <v>-7.810936838800007</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.278201225344523</v>
+        <v>1.373001319601794</v>
       </c>
       <c r="T88">
-        <v>4.41362300822366</v>
+        <v>4.753132470394712</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03350898940525206</v>
+        <v>0.03312382860749054</v>
       </c>
       <c r="W88">
-        <v>0.2278985802982416</v>
+        <v>0.2279894012143537</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1971117023838357</v>
+        <v>0.1948460506322973</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.376840950604721</v>
+        <v>0.378740950604721</v>
       </c>
       <c r="C89">
-        <v>-16.26329731082296</v>
+        <v>-18.88903716301755</v>
       </c>
       <c r="D89">
-        <v>69.20090268917708</v>
+        <v>68.85176283698249</v>
       </c>
       <c r="E89">
-        <v>190.2042</v>
+        <v>192.4808</v>
       </c>
       <c r="F89">
-        <v>198.0642</v>
+        <v>200.3408</v>
       </c>
       <c r="G89">
         <v>112.6</v>
@@ -8573,37 +8573,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M89">
-        <v>46.70353836000001</v>
+        <v>47.24036064000001</v>
       </c>
       <c r="N89">
-        <v>-37.60353836000001</v>
+        <v>-38.14036064</v>
       </c>
       <c r="O89">
-        <v>-6.392601521200002</v>
+        <v>-6.483861308800001</v>
       </c>
       <c r="P89">
-        <v>-31.21093683880001</v>
+        <v>-31.6564993312</v>
       </c>
       <c r="Q89">
-        <v>-7.810936838800007</v>
+        <v>-8.256499331200004</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.373001319601794</v>
+        <v>1.483601429568611</v>
       </c>
       <c r="T89">
-        <v>4.753132470394712</v>
+        <v>5.149226842927605</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03312382860749054</v>
+        <v>0.03274742146422361</v>
       </c>
       <c r="W89">
-        <v>0.2279894012143537</v>
+        <v>0.2280781580187361</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1948460506322973</v>
+        <v>0.1926318909660212</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.378740950604721</v>
+        <v>0.380640950604721</v>
       </c>
       <c r="C90">
-        <v>-18.88903716301755</v>
+        <v>-21.51127166476414</v>
       </c>
       <c r="D90">
-        <v>68.85176283698249</v>
+        <v>68.50612833523589</v>
       </c>
       <c r="E90">
-        <v>192.4808</v>
+        <v>194.7574</v>
       </c>
       <c r="F90">
-        <v>200.3408</v>
+        <v>202.6174</v>
       </c>
       <c r="G90">
         <v>112.6</v>
@@ -8655,37 +8655,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M90">
-        <v>47.24036064000001</v>
+        <v>47.77718292000001</v>
       </c>
       <c r="N90">
-        <v>-38.14036064</v>
+        <v>-38.67718292000001</v>
       </c>
       <c r="O90">
-        <v>-6.483861308800001</v>
+        <v>-6.575121096400002</v>
       </c>
       <c r="P90">
-        <v>-31.6564993312</v>
+        <v>-32.1020618236</v>
       </c>
       <c r="Q90">
-        <v>-8.256499331200004</v>
+        <v>-8.702061823600005</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.483601429568611</v>
+        <v>1.614310650438484</v>
       </c>
       <c r="T90">
-        <v>5.149226842927605</v>
+        <v>5.617338374102841</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03274742146422361</v>
+        <v>0.03237947290844582</v>
       </c>
       <c r="W90">
-        <v>0.2280781580187361</v>
+        <v>0.2281649202881885</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1926318909660212</v>
+        <v>0.19046748769674</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.380640950604721</v>
+        <v>0.382540950604721</v>
       </c>
       <c r="C91">
-        <v>-21.51127166476414</v>
+        <v>-24.13005334275172</v>
       </c>
       <c r="D91">
-        <v>68.50612833523589</v>
+        <v>68.16394665724833</v>
       </c>
       <c r="E91">
-        <v>194.7574</v>
+        <v>197.034</v>
       </c>
       <c r="F91">
-        <v>202.6174</v>
+        <v>204.894</v>
       </c>
       <c r="G91">
         <v>112.6</v>
@@ -8737,37 +8737,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M91">
-        <v>47.77718292000001</v>
+        <v>48.31400520000001</v>
       </c>
       <c r="N91">
-        <v>-38.67718292000001</v>
+        <v>-39.21400520000001</v>
       </c>
       <c r="O91">
-        <v>-6.575121096400002</v>
+        <v>-6.666380884000002</v>
       </c>
       <c r="P91">
-        <v>-32.1020618236</v>
+        <v>-32.54762431600001</v>
       </c>
       <c r="Q91">
-        <v>-8.702061823600005</v>
+        <v>-9.147624316000012</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.614310650438484</v>
+        <v>1.771161715482333</v>
       </c>
       <c r="T91">
-        <v>5.617338374102841</v>
+        <v>6.179072211513127</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03237947290844582</v>
+        <v>0.03201970098724086</v>
       </c>
       <c r="W91">
-        <v>0.2281649202881885</v>
+        <v>0.2282497545072086</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.19046748769674</v>
+        <v>0.1883511822778874</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.382540950604721</v>
+        <v>0.384440950604721</v>
       </c>
       <c r="C92">
-        <v>-24.13005334275172</v>
+        <v>-26.74543367942158</v>
       </c>
       <c r="D92">
-        <v>68.16394665724833</v>
+        <v>67.82516632057846</v>
       </c>
       <c r="E92">
-        <v>197.034</v>
+        <v>199.3106</v>
       </c>
       <c r="F92">
-        <v>204.894</v>
+        <v>207.1706</v>
       </c>
       <c r="G92">
         <v>112.6</v>
@@ -8819,37 +8819,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M92">
-        <v>48.31400520000001</v>
+        <v>48.85082748000001</v>
       </c>
       <c r="N92">
-        <v>-39.21400520000001</v>
+        <v>-39.75082748000001</v>
       </c>
       <c r="O92">
-        <v>-6.666380884000002</v>
+        <v>-6.757640671600003</v>
       </c>
       <c r="P92">
-        <v>-32.54762431600001</v>
+        <v>-32.99318680840001</v>
       </c>
       <c r="Q92">
-        <v>-9.147624316000012</v>
+        <v>-9.593186808400013</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.771161715482333</v>
+        <v>1.962868572758148</v>
       </c>
       <c r="T92">
-        <v>6.179072211513127</v>
+        <v>6.865635790570141</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03201970098724086</v>
+        <v>0.03166783614122722</v>
       </c>
       <c r="W92">
-        <v>0.2282497545072086</v>
+        <v>0.2283327242378986</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1883511822778874</v>
+        <v>0.1862813890660424</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.384440950604721</v>
+        <v>0.3863409506047211</v>
       </c>
       <c r="C93">
-        <v>-26.74543367942158</v>
+        <v>-29.35746313878917</v>
       </c>
       <c r="D93">
-        <v>67.82516632057846</v>
+        <v>67.48973686121087</v>
       </c>
       <c r="E93">
-        <v>199.3106</v>
+        <v>201.5872</v>
       </c>
       <c r="F93">
-        <v>207.1706</v>
+        <v>209.4472</v>
       </c>
       <c r="G93">
         <v>112.6</v>
@@ -8901,37 +8901,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M93">
-        <v>48.85082748000001</v>
+        <v>49.38764976000001</v>
       </c>
       <c r="N93">
-        <v>-39.75082748000001</v>
+        <v>-40.28764976000001</v>
       </c>
       <c r="O93">
-        <v>-6.757640671600003</v>
+        <v>-6.848900459200002</v>
       </c>
       <c r="P93">
-        <v>-32.99318680840001</v>
+        <v>-33.4387493008</v>
       </c>
       <c r="Q93">
-        <v>-9.593186808400013</v>
+        <v>-10.03874930080001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.962868572758148</v>
+        <v>2.202502144352917</v>
       </c>
       <c r="T93">
-        <v>6.865635790570141</v>
+        <v>7.723840264391411</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03166783614122722</v>
+        <v>0.03132362053099649</v>
       </c>
       <c r="W93">
-        <v>0.2283327242378986</v>
+        <v>0.2284138902787911</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1862813890660424</v>
+        <v>0.1842565913588029</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3863409506047211</v>
+        <v>0.388240950604721</v>
       </c>
       <c r="C94">
-        <v>-29.35746313878917</v>
+        <v>-31.96619119150313</v>
       </c>
       <c r="D94">
-        <v>67.48973686121087</v>
+        <v>67.15760880849693</v>
       </c>
       <c r="E94">
-        <v>201.5872</v>
+        <v>203.8638</v>
       </c>
       <c r="F94">
-        <v>209.4472</v>
+        <v>211.7238</v>
       </c>
       <c r="G94">
         <v>112.6</v>
@@ -8983,37 +8983,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M94">
-        <v>49.38764976000001</v>
+        <v>49.92447204000001</v>
       </c>
       <c r="N94">
-        <v>-40.28764976000001</v>
+        <v>-40.82447204000001</v>
       </c>
       <c r="O94">
-        <v>-6.848900459200002</v>
+        <v>-6.940160246800002</v>
       </c>
       <c r="P94">
-        <v>-33.4387493008</v>
+        <v>-33.88431179320001</v>
       </c>
       <c r="Q94">
-        <v>-10.03874930080001</v>
+        <v>-10.48431179320001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>2.202502144352917</v>
+        <v>2.510602450689048</v>
       </c>
       <c r="T94">
-        <v>7.723840264391411</v>
+        <v>8.827246016447328</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03132362053099649</v>
+        <v>0.03098680740700728</v>
       </c>
       <c r="W94">
-        <v>0.2284138902787911</v>
+        <v>0.2284933108134277</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1842565913588029</v>
+        <v>0.1822753376882781</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.388240950604721</v>
+        <v>0.390140950604721</v>
       </c>
       <c r="C95">
-        <v>-31.96619119150313</v>
+        <v>-34.57166633916827</v>
       </c>
       <c r="D95">
-        <v>67.15760880849693</v>
+        <v>66.82873366083177</v>
       </c>
       <c r="E95">
-        <v>203.8638</v>
+        <v>206.1404</v>
       </c>
       <c r="F95">
-        <v>211.7238</v>
+        <v>214.0004</v>
       </c>
       <c r="G95">
         <v>112.6</v>
@@ -9065,37 +9065,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M95">
-        <v>49.92447204000001</v>
+        <v>50.46129432000001</v>
       </c>
       <c r="N95">
-        <v>-40.82447204000001</v>
+        <v>-41.36129432000001</v>
       </c>
       <c r="O95">
-        <v>-6.940160246800002</v>
+        <v>-7.031420034400003</v>
       </c>
       <c r="P95">
-        <v>-33.88431179320001</v>
+        <v>-34.32987428560001</v>
       </c>
       <c r="Q95">
-        <v>-10.48431179320001</v>
+        <v>-10.92987428560001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>2.510602450689048</v>
+        <v>2.921402859137224</v>
       </c>
       <c r="T95">
-        <v>8.827246016447328</v>
+        <v>10.29845368585522</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03098680740700728</v>
+        <v>0.03065716051969869</v>
       </c>
       <c r="W95">
-        <v>0.2284933108134277</v>
+        <v>0.2285710415494551</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1822753376882781</v>
+        <v>0.1803362383511687</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.390140950604721</v>
+        <v>0.3920409506047211</v>
       </c>
       <c r="C96">
-        <v>-34.57166633916827</v>
+        <v>-37.17393613795727</v>
       </c>
       <c r="D96">
-        <v>66.82873366083177</v>
+        <v>66.50306386204278</v>
       </c>
       <c r="E96">
-        <v>206.1404</v>
+        <v>208.417</v>
       </c>
       <c r="F96">
-        <v>214.0004</v>
+        <v>216.277</v>
       </c>
       <c r="G96">
         <v>112.6</v>
@@ -9147,37 +9147,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M96">
-        <v>50.46129432000001</v>
+        <v>50.99811660000001</v>
       </c>
       <c r="N96">
-        <v>-41.36129432000001</v>
+        <v>-41.89811660000001</v>
       </c>
       <c r="O96">
-        <v>-7.031420034400003</v>
+        <v>-7.122679822000002</v>
       </c>
       <c r="P96">
-        <v>-34.32987428560001</v>
+        <v>-34.77543677800001</v>
       </c>
       <c r="Q96">
-        <v>-10.92987428560001</v>
+        <v>-11.37543677800001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.921402859137224</v>
+        <v>3.49652343096467</v>
       </c>
       <c r="T96">
-        <v>10.29845368585522</v>
+        <v>12.35814442302627</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03065716051969869</v>
+        <v>0.03033445356685976</v>
       </c>
       <c r="W96">
-        <v>0.2285710415494551</v>
+        <v>0.2286471358489345</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1803362383511687</v>
+        <v>0.1784379621579986</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3920409506047211</v>
+        <v>0.393940950604721</v>
       </c>
       <c r="C97">
-        <v>-37.17393613795727</v>
+        <v>-39.77304722153534</v>
       </c>
       <c r="D97">
-        <v>66.50306386204278</v>
+        <v>66.1805527784647</v>
       </c>
       <c r="E97">
-        <v>208.417</v>
+        <v>210.6936</v>
       </c>
       <c r="F97">
-        <v>216.277</v>
+        <v>218.5536</v>
       </c>
       <c r="G97">
         <v>112.6</v>
@@ -9229,37 +9229,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M97">
-        <v>50.99811660000001</v>
+        <v>51.53493888000001</v>
       </c>
       <c r="N97">
-        <v>-41.89811660000001</v>
+        <v>-42.43493888000001</v>
       </c>
       <c r="O97">
-        <v>-7.122679822000002</v>
+        <v>-7.213939609600002</v>
       </c>
       <c r="P97">
-        <v>-34.77543677800001</v>
+        <v>-35.22099927040001</v>
       </c>
       <c r="Q97">
-        <v>-11.37543677800001</v>
+        <v>-11.82099927040001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>3.49652343096467</v>
+        <v>4.359204288705839</v>
       </c>
       <c r="T97">
-        <v>12.35814442302627</v>
+        <v>15.44768052878284</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03033445356685976</v>
+        <v>0.0300184696755383</v>
       </c>
       <c r="W97">
-        <v>0.2286471358489345</v>
+        <v>0.2287216448505081</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1784379621579986</v>
+        <v>0.1765792333855194</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.393940950604721</v>
+        <v>0.395840950604721</v>
       </c>
       <c r="C98">
-        <v>-39.77304722153531</v>
+        <v>-42.36904532332119</v>
       </c>
       <c r="D98">
-        <v>66.1805527784647</v>
+        <v>65.86115467667884</v>
       </c>
       <c r="E98">
-        <v>210.6936</v>
+        <v>212.9702</v>
       </c>
       <c r="F98">
-        <v>218.5536</v>
+        <v>220.8302</v>
       </c>
       <c r="G98">
         <v>112.6</v>
@@ -9311,37 +9311,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M98">
-        <v>51.53493888000001</v>
+        <v>52.07176116000001</v>
       </c>
       <c r="N98">
-        <v>-42.43493888</v>
+        <v>-42.97176116000001</v>
       </c>
       <c r="O98">
-        <v>-7.213939609600001</v>
+        <v>-7.305199397200002</v>
       </c>
       <c r="P98">
-        <v>-35.2209992704</v>
+        <v>-35.66656176280001</v>
       </c>
       <c r="Q98">
-        <v>-11.8209992704</v>
+        <v>-12.26656176280001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>4.359204288705828</v>
+        <v>5.797005718274437</v>
       </c>
       <c r="T98">
-        <v>15.4476805287828</v>
+        <v>20.5969073717104</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03001846967553831</v>
+        <v>0.02970900091599667</v>
       </c>
       <c r="W98">
-        <v>0.2287216448505081</v>
+        <v>0.228794617584008</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1765792333855194</v>
+        <v>0.1747588289176275</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.395840950604721</v>
+        <v>0.397740950604721</v>
       </c>
       <c r="C99">
-        <v>-42.36904532332119</v>
+        <v>-44.96197529810621</v>
       </c>
       <c r="D99">
-        <v>65.86115467667884</v>
+        <v>65.5448247018938</v>
       </c>
       <c r="E99">
-        <v>212.9702</v>
+        <v>215.2468</v>
       </c>
       <c r="F99">
-        <v>220.8302</v>
+        <v>223.1068</v>
       </c>
       <c r="G99">
         <v>112.6</v>
@@ -9393,37 +9393,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M99">
-        <v>52.07176116000001</v>
+        <v>52.60858344</v>
       </c>
       <c r="N99">
-        <v>-42.97176116000001</v>
+        <v>-43.50858344</v>
       </c>
       <c r="O99">
-        <v>-7.305199397200002</v>
+        <v>-7.396459184800001</v>
       </c>
       <c r="P99">
-        <v>-35.66656176280001</v>
+        <v>-36.1121242552</v>
       </c>
       <c r="Q99">
-        <v>-12.26656176280001</v>
+        <v>-12.7121242552</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>5.797005718274437</v>
+        <v>8.672608577411657</v>
       </c>
       <c r="T99">
-        <v>20.5969073717104</v>
+        <v>30.8953610575656</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02970900091599667</v>
+        <v>0.02940584784542528</v>
       </c>
       <c r="W99">
-        <v>0.228794617584008</v>
+        <v>0.2288661010780487</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1747588289176275</v>
+        <v>0.1729755755613251</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.397740950604721</v>
+        <v>0.399640950604721</v>
       </c>
       <c r="C100">
-        <v>-44.96197529810621</v>
+        <v>-47.55188114305392</v>
       </c>
       <c r="D100">
-        <v>65.5448247018938</v>
+        <v>65.2315188569461</v>
       </c>
       <c r="E100">
-        <v>215.2468</v>
+        <v>217.5234</v>
       </c>
       <c r="F100">
-        <v>223.1068</v>
+        <v>225.3834</v>
       </c>
       <c r="G100">
         <v>112.6</v>
@@ -9475,37 +9475,37 @@
         <v>9.100000000000001</v>
       </c>
       <c r="M100">
-        <v>52.60858344</v>
+        <v>53.14540572000001</v>
       </c>
       <c r="N100">
-        <v>-43.50858344</v>
+        <v>-44.04540572000001</v>
       </c>
       <c r="O100">
-        <v>-7.396459184800001</v>
+        <v>-7.487718972400002</v>
       </c>
       <c r="P100">
-        <v>-36.1121242552</v>
+        <v>-36.5576867476</v>
       </c>
       <c r="Q100">
-        <v>-12.7121242552</v>
+        <v>-13.1576867476</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>8.672608577411657</v>
+        <v>17.29941715482331</v>
       </c>
       <c r="T100">
-        <v>30.8953610575656</v>
+        <v>61.7907221151312</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02940584784542528</v>
+        <v>0.02910881907930987</v>
       </c>
       <c r="W100">
-        <v>0.2288661010780487</v>
+        <v>0.2289361404610988</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1729755755613251</v>
+        <v>0.1712283475253522</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.399640950604721</v>
-      </c>
-      <c r="C101">
-        <v>-47.55188114305392</v>
-      </c>
-      <c r="D101">
-        <v>65.2315188569461</v>
-      </c>
-      <c r="E101">
-        <v>217.5234</v>
-      </c>
-      <c r="F101">
-        <v>225.3834</v>
-      </c>
-      <c r="G101">
-        <v>112.6</v>
-      </c>
-      <c r="H101">
-        <v>219.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>32.5</v>
-      </c>
-      <c r="K101">
-        <v>23.4</v>
-      </c>
-      <c r="L101">
-        <v>9.100000000000001</v>
-      </c>
-      <c r="M101">
-        <v>53.14540572000001</v>
-      </c>
-      <c r="N101">
-        <v>-44.04540572000001</v>
-      </c>
-      <c r="O101">
-        <v>-7.487718972400002</v>
-      </c>
-      <c r="P101">
-        <v>-36.5576867476</v>
-      </c>
-      <c r="Q101">
-        <v>-13.1576867476</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>17.29941715482331</v>
-      </c>
-      <c r="T101">
-        <v>61.7907221151312</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02910881907930987</v>
-      </c>
-      <c r="W101">
-        <v>0.2289361404610988</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1712283475253522</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
